--- a/data/portfolio_tracker.xlsx
+++ b/data/portfolio_tracker.xlsx
@@ -561,7 +561,7 @@
         <v>0.32</v>
       </c>
       <c r="H3" t="n">
-        <v>397741</v>
+        <v>397841</v>
       </c>
       <c r="I3" t="n">
         <v>856388</v>
@@ -681,7 +681,7 @@
         <v>-6.7</v>
       </c>
       <c r="H5" t="n">
-        <v>11105461</v>
+        <v>11116049</v>
       </c>
       <c r="I5" t="n">
         <v>17541602</v>
@@ -741,7 +741,7 @@
         <v>-10.77</v>
       </c>
       <c r="H6" t="n">
-        <v>567640</v>
+        <v>567956</v>
       </c>
       <c r="I6" t="n">
         <v>236487</v>
@@ -801,7 +801,7 @@
         <v>-9.449999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>9596321</v>
+        <v>9596521</v>
       </c>
       <c r="I7" t="n">
         <v>14339627</v>
@@ -861,7 +861,7 @@
         <v>11.28</v>
       </c>
       <c r="H8" t="n">
-        <v>128405</v>
+        <v>128509</v>
       </c>
       <c r="I8" t="n">
         <v>249886</v>
@@ -988,7 +988,7 @@
         <v>-5.95</v>
       </c>
       <c r="H11" t="n">
-        <v>1527780</v>
+        <v>1528118</v>
       </c>
       <c r="I11" t="n">
         <v>992989</v>
@@ -1048,7 +1048,7 @@
         <v>12.43</v>
       </c>
       <c r="H12" t="n">
-        <v>19191666</v>
+        <v>19203049</v>
       </c>
       <c r="I12" t="n">
         <v>18011981</v>
@@ -1129,10 +1129,10 @@
         <v>5.53</v>
       </c>
       <c r="O13" t="n">
-        <v>9.31</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-42.21</v>
+        <v>-40.55</v>
       </c>
       <c r="Q13" t="n">
         <v>4.18</v>
@@ -1262,22 +1262,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>104.96</v>
+        <v>107</v>
       </c>
       <c r="D19" t="n">
-        <v>107.63</v>
+        <v>104.61</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.48</v>
+        <v>2.28</v>
       </c>
       <c r="F19" t="n">
-        <v>9.880000000000001</v>
+        <v>11.13</v>
       </c>
       <c r="G19" t="n">
-        <v>17.96</v>
+        <v>22.89</v>
       </c>
       <c r="H19" t="n">
-        <v>2.01</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="20">
@@ -1292,22 +1292,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4426.3</v>
+        <v>4337.1</v>
       </c>
       <c r="D20" t="n">
-        <v>4364.5</v>
+        <v>4366.2</v>
       </c>
       <c r="E20" t="n">
-        <v>1.42</v>
+        <v>-0.67</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.46</v>
+        <v>-2.09</v>
       </c>
       <c r="G20" t="n">
-        <v>0.39</v>
+        <v>-0.61</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.17</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="21">
@@ -1322,22 +1322,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>52521.97</v>
+        <v>52506.94</v>
       </c>
       <c r="D21" t="n">
-        <v>52064.1</v>
+        <v>52573.29</v>
       </c>
       <c r="E21" t="n">
-        <v>0.88</v>
+        <v>-0.13</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.17</v>
+        <v>-1.7</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.32</v>
+        <v>-2.48</v>
       </c>
       <c r="H21" t="n">
-        <v>1.15</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="22">
@@ -1352,22 +1352,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>12.28</v>
+        <v>12.29</v>
       </c>
       <c r="D22" t="n">
         <v>11.8</v>
       </c>
       <c r="E22" t="n">
-        <v>4.07</v>
+        <v>4.15</v>
       </c>
       <c r="F22" t="n">
-        <v>14.98</v>
+        <v>15.07</v>
       </c>
       <c r="G22" t="n">
-        <v>7.53</v>
-      </c>
-      <c r="H22" t="n">
-        <v/>
+        <v>7.62</v>
       </c>
     </row>
   </sheetData>
@@ -2283,7 +2280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3172,6 +3169,29 @@
       </c>
       <c r="G38" t="n">
         <v>2.01</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B39" t="n">
+        <v>107</v>
+      </c>
+      <c r="C39" t="n">
+        <v>104.61</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="E39" t="n">
+        <v>11.13</v>
+      </c>
+      <c r="F39" t="n">
+        <v>22.89</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2.87</v>
       </c>
     </row>
   </sheetData>
@@ -3185,7 +3205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4074,6 +4094,29 @@
       </c>
       <c r="G38" t="n">
         <v>-0.17</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B39" t="n">
+        <v>4337.1</v>
+      </c>
+      <c r="C39" t="n">
+        <v>4366.2</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>
@@ -4087,7 +4130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4938,6 +4981,29 @@
       </c>
       <c r="G37" t="n">
         <v>1.15</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B38" t="n">
+        <v>52506.94</v>
+      </c>
+      <c r="C38" t="n">
+        <v>52573.29</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-2.48</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>
@@ -5748,9 +5814,6 @@
       <c r="F38" t="n">
         <v>7.53</v>
       </c>
-      <c r="G38" t="n">
-        <v/>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/portfolio_tracker.xlsx
+++ b/data/portfolio_tracker.xlsx
@@ -546,52 +546,52 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>432.6</v>
+      </c>
+      <c r="D3" t="n">
         <v>455.45</v>
       </c>
-      <c r="D3" t="n">
-        <v>454.65</v>
-      </c>
       <c r="E3" t="n">
-        <v>0.18</v>
+        <v>-5.02</v>
       </c>
       <c r="F3" t="n">
-        <v>-16.32</v>
+        <v>-11.33</v>
       </c>
       <c r="G3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>406386</v>
+      </c>
+      <c r="I3" t="n">
+        <v>397841</v>
+      </c>
+      <c r="J3" t="n">
         <v>0.32</v>
       </c>
-      <c r="H3" t="n">
-        <v>397841</v>
-      </c>
-      <c r="I3" t="n">
-        <v>856388</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.31</v>
-      </c>
       <c r="K3" t="n">
-        <v>-0.42</v>
+        <v>0.59</v>
       </c>
       <c r="L3" t="n">
-        <v>49.2</v>
+        <v>44</v>
       </c>
       <c r="M3" t="n">
-        <v>346.05</v>
+        <v>346.52</v>
       </c>
       <c r="N3" t="n">
-        <v>427.19</v>
+        <v>428.6</v>
       </c>
       <c r="O3" t="n">
         <v>544.3</v>
       </c>
       <c r="P3" t="n">
-        <v>-16.32</v>
+        <v>-20.52</v>
       </c>
       <c r="Q3" t="n">
         <v>240.57</v>
       </c>
       <c r="R3" t="n">
-        <v>89.31999999999999</v>
+        <v>79.81999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -606,52 +606,52 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>45</v>
+      </c>
+      <c r="D4" t="n">
         <v>46.18</v>
       </c>
-      <c r="D4" t="n">
-        <v>46.08</v>
-      </c>
       <c r="E4" t="n">
-        <v>0.22</v>
+        <v>-2.56</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.35</v>
+        <v>-3.31</v>
       </c>
       <c r="G4" t="n">
-        <v>1.14</v>
+        <v>-1.62</v>
       </c>
       <c r="H4" t="n">
+        <v>12741432</v>
+      </c>
+      <c r="I4" t="n">
         <v>5755589</v>
       </c>
-      <c r="I4" t="n">
-        <v>5591541</v>
-      </c>
       <c r="J4" t="n">
-        <v>0.72</v>
+        <v>1.58</v>
       </c>
       <c r="K4" t="n">
-        <v>-3</v>
+        <v>0.97</v>
       </c>
       <c r="L4" t="n">
-        <v>51.1</v>
+        <v>42.6</v>
       </c>
       <c r="M4" t="n">
-        <v>41.76</v>
+        <v>41.79</v>
       </c>
       <c r="N4" t="n">
-        <v>45.91</v>
+        <v>45.88</v>
       </c>
       <c r="O4" t="n">
         <v>48.02</v>
       </c>
       <c r="P4" t="n">
-        <v>-3.83</v>
+        <v>-6.29</v>
       </c>
       <c r="Q4" t="n">
         <v>28.36</v>
       </c>
       <c r="R4" t="n">
-        <v>62.83</v>
+        <v>58.67</v>
       </c>
     </row>
     <row r="5">
@@ -666,52 +666,52 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>258</v>
+      </c>
+      <c r="D5" t="n">
         <v>259.85</v>
       </c>
-      <c r="D5" t="n">
-        <v>259.3</v>
-      </c>
       <c r="E5" t="n">
-        <v>0.21</v>
+        <v>-0.71</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.61</v>
+        <v>-2.09</v>
       </c>
       <c r="G5" t="n">
-        <v>-6.7</v>
+        <v>-7.26</v>
       </c>
       <c r="H5" t="n">
+        <v>12129366</v>
+      </c>
+      <c r="I5" t="n">
         <v>11116049</v>
       </c>
-      <c r="I5" t="n">
-        <v>17541602</v>
-      </c>
       <c r="J5" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.93</v>
+        <v>0.79</v>
       </c>
       <c r="L5" t="n">
-        <v>36.1</v>
+        <v>34.1</v>
       </c>
       <c r="M5" t="n">
-        <v>304.21</v>
+        <v>303.57</v>
       </c>
       <c r="N5" t="n">
-        <v>275.9</v>
+        <v>275.29</v>
       </c>
       <c r="O5" t="n">
         <v>401.99</v>
       </c>
       <c r="P5" t="n">
-        <v>-35.36</v>
+        <v>-35.82</v>
       </c>
       <c r="Q5" t="n">
         <v>255.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="6">
@@ -726,52 +726,52 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>819.15</v>
+      </c>
+      <c r="D6" t="n">
         <v>815.35</v>
       </c>
-      <c r="D6" t="n">
-        <v>818.65</v>
-      </c>
       <c r="E6" t="n">
-        <v>-0.4</v>
+        <v>0.47</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.74</v>
+        <v>-1.15</v>
       </c>
       <c r="G6" t="n">
-        <v>-10.77</v>
+        <v>-13.78</v>
       </c>
       <c r="H6" t="n">
+        <v>434610</v>
+      </c>
+      <c r="I6" t="n">
         <v>567956</v>
       </c>
-      <c r="I6" t="n">
-        <v>236487</v>
-      </c>
       <c r="J6" t="n">
-        <v>1.09</v>
+        <v>0.88</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.7</v>
+        <v>0.43</v>
       </c>
       <c r="L6" t="n">
-        <v>26.3</v>
+        <v>28.8</v>
       </c>
       <c r="M6" t="n">
-        <v>946.9299999999999</v>
+        <v>946.4</v>
       </c>
       <c r="N6" t="n">
-        <v>905.76</v>
+        <v>903.55</v>
       </c>
       <c r="O6" t="n">
         <v>1203.96</v>
       </c>
       <c r="P6" t="n">
-        <v>-32.28</v>
+        <v>-31.96</v>
       </c>
       <c r="Q6" t="n">
         <v>788.84</v>
       </c>
       <c r="R6" t="n">
-        <v>3.36</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="7">
@@ -786,52 +786,52 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>64.06999999999999</v>
+      </c>
+      <c r="D7" t="n">
         <v>65.54000000000001</v>
       </c>
-      <c r="D7" t="n">
-        <v>66.52</v>
-      </c>
       <c r="E7" t="n">
-        <v>-1.47</v>
+        <v>-2.24</v>
       </c>
       <c r="F7" t="n">
-        <v>4.05</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>-9.449999999999999</v>
+        <v>-10</v>
       </c>
       <c r="H7" t="n">
+        <v>7608189</v>
+      </c>
+      <c r="I7" t="n">
         <v>9596521</v>
       </c>
-      <c r="I7" t="n">
-        <v>14339627</v>
-      </c>
       <c r="J7" t="n">
-        <v>0.64</v>
+        <v>0.5</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.67</v>
+        <v>0.42</v>
       </c>
       <c r="L7" t="n">
-        <v>44.2</v>
+        <v>40.2</v>
       </c>
       <c r="M7" t="n">
-        <v>59.65</v>
+        <v>59.69</v>
       </c>
       <c r="N7" t="n">
-        <v>67.75</v>
+        <v>67.84</v>
       </c>
       <c r="O7" t="n">
         <v>72.47</v>
       </c>
       <c r="P7" t="n">
-        <v>-9.56</v>
+        <v>-11.59</v>
       </c>
       <c r="Q7" t="n">
         <v>44.18</v>
       </c>
       <c r="R7" t="n">
-        <v>48.35</v>
+        <v>45.02</v>
       </c>
     </row>
     <row r="8">
@@ -846,52 +846,52 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>981.8</v>
+      </c>
+      <c r="D8" t="n">
         <v>966.3</v>
       </c>
-      <c r="D8" t="n">
-        <v>977.2</v>
-      </c>
       <c r="E8" t="n">
-        <v>-1.12</v>
+        <v>1.6</v>
       </c>
       <c r="F8" t="n">
-        <v>0.42</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>11.28</v>
+        <v>16.24</v>
       </c>
       <c r="H8" t="n">
+        <v>693725</v>
+      </c>
+      <c r="I8" t="n">
         <v>128509</v>
       </c>
-      <c r="I8" t="n">
-        <v>249886</v>
-      </c>
       <c r="J8" t="n">
-        <v>0.29</v>
+        <v>1.61</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.58</v>
+        <v>7.94</v>
       </c>
       <c r="L8" t="n">
-        <v>59.4</v>
+        <v>62.3</v>
       </c>
       <c r="M8" t="n">
-        <v>763.11</v>
+        <v>764.15</v>
       </c>
       <c r="N8" t="n">
-        <v>879.5700000000001</v>
+        <v>881.91</v>
       </c>
       <c r="O8" t="n">
         <v>1001.9</v>
       </c>
       <c r="P8" t="n">
-        <v>-3.55</v>
+        <v>-2.01</v>
       </c>
       <c r="Q8" t="n">
         <v>550.47</v>
       </c>
       <c r="R8" t="n">
-        <v>75.54000000000001</v>
+        <v>78.36</v>
       </c>
     </row>
     <row r="9">
@@ -916,25 +916,25 @@
         <v>6.51</v>
       </c>
       <c r="D10" t="n">
-        <v>6.72</v>
+        <v>6.51</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.12</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.76</v>
+        <v>-5.38</v>
       </c>
       <c r="G10" t="n">
-        <v>-17.8</v>
+        <v>-20.61</v>
       </c>
       <c r="H10" t="n">
+        <v>3339</v>
+      </c>
+      <c r="I10" t="n">
         <v>10517</v>
       </c>
-      <c r="I10" t="n">
-        <v>5700</v>
-      </c>
       <c r="J10" t="n">
-        <v>3.71</v>
+        <v>1.01</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -943,10 +943,10 @@
         <v>36.1</v>
       </c>
       <c r="M10" t="n">
-        <v>8.640000000000001</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>7.06</v>
+        <v>7.07</v>
       </c>
       <c r="O10" t="n">
         <v>13.78</v>
@@ -973,52 +973,52 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>945</v>
+      </c>
+      <c r="D11" t="n">
         <v>974.2</v>
       </c>
-      <c r="D11" t="n">
-        <v>967.9</v>
-      </c>
       <c r="E11" t="n">
-        <v>0.65</v>
+        <v>-3</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.77</v>
+        <v>-4.55</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.95</v>
+        <v>-7.11</v>
       </c>
       <c r="H11" t="n">
+        <v>569734</v>
+      </c>
+      <c r="I11" t="n">
         <v>1528118</v>
       </c>
-      <c r="I11" t="n">
-        <v>992989</v>
-      </c>
       <c r="J11" t="n">
-        <v>1.52</v>
+        <v>0.54</v>
       </c>
       <c r="K11" t="n">
-        <v>0.85</v>
+        <v>-1.38</v>
       </c>
       <c r="L11" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="M11" t="n">
-        <v>935.25</v>
+        <v>935.03</v>
       </c>
       <c r="N11" t="n">
-        <v>1032.27</v>
+        <v>1030.71</v>
       </c>
       <c r="O11" t="n">
         <v>1117.2</v>
       </c>
       <c r="P11" t="n">
-        <v>-12.8</v>
+        <v>-15.41</v>
       </c>
       <c r="Q11" t="n">
         <v>682.6</v>
       </c>
       <c r="R11" t="n">
-        <v>42.72</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="12">
@@ -1033,52 +1033,52 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>23.49</v>
+      </c>
+      <c r="D12" t="n">
         <v>24.87</v>
       </c>
-      <c r="D12" t="n">
-        <v>24.82</v>
-      </c>
       <c r="E12" t="n">
-        <v>0.2</v>
+        <v>-5.55</v>
       </c>
       <c r="F12" t="n">
-        <v>3.45</v>
+        <v>-6.6</v>
       </c>
       <c r="G12" t="n">
-        <v>12.43</v>
+        <v>7.02</v>
       </c>
       <c r="H12" t="n">
+        <v>11641397</v>
+      </c>
+      <c r="I12" t="n">
         <v>19203049</v>
       </c>
-      <c r="I12" t="n">
-        <v>18011981</v>
-      </c>
       <c r="J12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.33</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.93</v>
+        <v>0.7</v>
       </c>
       <c r="L12" t="n">
-        <v>56.7</v>
+        <v>46.6</v>
       </c>
       <c r="M12" t="n">
-        <v>24.65</v>
+        <v>24.63</v>
       </c>
       <c r="N12" t="n">
-        <v>23.16</v>
+        <v>23.17</v>
       </c>
       <c r="O12" t="n">
         <v>32.31</v>
       </c>
       <c r="P12" t="n">
-        <v>-23.03</v>
+        <v>-27.3</v>
       </c>
       <c r="Q12" t="n">
         <v>21.49</v>
       </c>
       <c r="R12" t="n">
-        <v>15.73</v>
+        <v>9.31</v>
       </c>
     </row>
     <row r="13">
@@ -1093,37 +1093,37 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="D13" t="n">
         <v>5.38</v>
       </c>
-      <c r="D13" t="n">
-        <v>5.62</v>
-      </c>
       <c r="E13" t="n">
-        <v>-4.27</v>
+        <v>-0.19</v>
       </c>
       <c r="F13" t="n">
-        <v>-9.27</v>
+        <v>-8.98</v>
       </c>
       <c r="G13" t="n">
-        <v>1.13</v>
+        <v>-1.47</v>
       </c>
       <c r="H13" t="n">
+        <v>309218</v>
+      </c>
+      <c r="I13" t="n">
         <v>934016</v>
       </c>
-      <c r="I13" t="n">
-        <v>346180</v>
-      </c>
       <c r="J13" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.59</v>
+        <v>1.36</v>
       </c>
       <c r="L13" t="n">
-        <v>40.9</v>
+        <v>40.7</v>
       </c>
       <c r="M13" t="n">
-        <v>5.85</v>
+        <v>5.84</v>
       </c>
       <c r="N13" t="n">
         <v>5.53</v>
@@ -1132,13 +1132,13 @@
         <v>9.050000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-40.55</v>
+        <v>-40.66</v>
       </c>
       <c r="Q13" t="n">
         <v>4.18</v>
       </c>
       <c r="R13" t="n">
-        <v>28.71</v>
+        <v>28.47</v>
       </c>
     </row>
     <row r="15">
@@ -1202,22 +1202,22 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v>23118.6</v>
+      </c>
+      <c r="D17" t="n">
         <v>23398.1</v>
       </c>
-      <c r="D17" t="n">
-        <v>23477.8</v>
-      </c>
       <c r="E17" t="n">
-        <v>-0.34</v>
+        <v>-1.19</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.09</v>
+        <v>-2.78</v>
       </c>
       <c r="G17" t="n">
-        <v>-4.09</v>
+        <v>-5.12</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.88</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="18">
@@ -1232,22 +1232,22 @@
         </is>
       </c>
       <c r="C18" t="n">
+        <v>55794.75</v>
+      </c>
+      <c r="D18" t="n">
         <v>56606.55</v>
       </c>
-      <c r="D18" t="n">
-        <v>56471.95</v>
-      </c>
       <c r="E18" t="n">
-        <v>0.24</v>
+        <v>-1.43</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.33</v>
+        <v>-2.27</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.78</v>
+        <v>-2.95</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.51</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="19">
@@ -1262,22 +1262,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>107</v>
+        <v>103.3</v>
       </c>
       <c r="D19" t="n">
-        <v>104.61</v>
+        <v>105.68</v>
       </c>
       <c r="E19" t="n">
-        <v>2.28</v>
+        <v>-2.25</v>
       </c>
       <c r="F19" t="n">
-        <v>11.13</v>
+        <v>5.49</v>
       </c>
       <c r="G19" t="n">
-        <v>22.89</v>
+        <v>16.7</v>
       </c>
       <c r="H19" t="n">
-        <v>2.87</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="20">
@@ -1292,22 +1292,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4337.1</v>
+        <v>4316.9</v>
       </c>
       <c r="D20" t="n">
-        <v>4366.2</v>
+        <v>4351.9</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.67</v>
+        <v>-0.8</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.09</v>
+        <v>-2.75</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.61</v>
+        <v>-2.71</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="21">
@@ -1322,22 +1322,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>52506.94</v>
+        <v>51895.07</v>
       </c>
       <c r="D21" t="n">
-        <v>52573.29</v>
+        <v>52421.2</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.13</v>
+        <v>-1</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7</v>
+        <v>-1.69</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.48</v>
+        <v>-3.42</v>
       </c>
       <c r="H21" t="n">
-        <v>1.39</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="22">
@@ -1352,19 +1352,22 @@
         </is>
       </c>
       <c r="C22" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="D22" t="n">
         <v>12.29</v>
       </c>
-      <c r="D22" t="n">
-        <v>11.8</v>
-      </c>
       <c r="E22" t="n">
-        <v>4.15</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>15.07</v>
+        <v>20.34</v>
       </c>
       <c r="G22" t="n">
-        <v>7.62</v>
+        <v>18.74</v>
+      </c>
+      <c r="H22" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1378,7 +1381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2267,6 +2270,29 @@
       </c>
       <c r="G38" t="n">
         <v>-2.51</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B39" t="n">
+        <v>55794.75</v>
+      </c>
+      <c r="C39" t="n">
+        <v>56606.55</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-1.43</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-2.27</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-2.95</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>
@@ -2280,7 +2306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3192,6 +3218,29 @@
       </c>
       <c r="G39" t="n">
         <v>2.87</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B40" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="C40" t="n">
+        <v>105.68</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="E40" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="F40" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.68</v>
       </c>
     </row>
   </sheetData>
@@ -3205,7 +3254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4117,6 +4166,29 @@
       </c>
       <c r="G39" t="n">
         <v>0.3</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B40" t="n">
+        <v>4316.9</v>
+      </c>
+      <c r="C40" t="n">
+        <v>4351.9</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="F40" t="n">
+        <v>-2.71</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-0.51</v>
       </c>
     </row>
   </sheetData>
@@ -4130,7 +4202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5004,6 +5076,29 @@
       </c>
       <c r="G38" t="n">
         <v>1.39</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B39" t="n">
+        <v>51895.07</v>
+      </c>
+      <c r="C39" t="n">
+        <v>52421.2</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-1.69</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-3.42</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-0.89</v>
       </c>
     </row>
   </sheetData>
@@ -5017,7 +5112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5813,6 +5908,29 @@
       </c>
       <c r="F38" t="n">
         <v>7.53</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B39" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="C39" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="D39" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="E39" t="n">
+        <v>20.34</v>
+      </c>
+      <c r="F39" t="n">
+        <v>18.74</v>
+      </c>
+      <c r="G39" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -5826,7 +5944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q37"/>
+  <dimension ref="A1:Q38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7740,6 +7858,59 @@
         <v>5.29</v>
       </c>
       <c r="Q37" t="n">
+        <v>23.06</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B38" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="C38" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-5.38</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-20.61</v>
+      </c>
+      <c r="G38" t="n">
+        <v>3339</v>
+      </c>
+      <c r="H38" t="n">
+        <v>10517</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="L38" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="M38" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="N38" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="O38" t="n">
+        <v>-52.76</v>
+      </c>
+      <c r="P38" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="Q38" t="n">
         <v>23.06</v>
       </c>
     </row>
@@ -7754,7 +7925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q37"/>
+  <dimension ref="A1:Q38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9669,6 +9840,59 @@
       </c>
       <c r="Q37" t="n">
         <v>15.73</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B38" t="n">
+        <v>23.49</v>
+      </c>
+      <c r="C38" t="n">
+        <v>24.87</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-5.55</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="F38" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="G38" t="n">
+        <v>11641397</v>
+      </c>
+      <c r="H38" t="n">
+        <v>19203049</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K38" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="L38" t="n">
+        <v>24.63</v>
+      </c>
+      <c r="M38" t="n">
+        <v>23.17</v>
+      </c>
+      <c r="N38" t="n">
+        <v>32.31</v>
+      </c>
+      <c r="O38" t="n">
+        <v>-27.3</v>
+      </c>
+      <c r="P38" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>9.31</v>
       </c>
     </row>
   </sheetData>
@@ -9682,7 +9906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q35"/>
+  <dimension ref="A1:Q36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11491,6 +11715,59 @@
       </c>
       <c r="Q35" t="n">
         <v>62.83</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B36" t="n">
+        <v>45</v>
+      </c>
+      <c r="C36" t="n">
+        <v>46.18</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-2.56</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-3.31</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-1.62</v>
+      </c>
+      <c r="G36" t="n">
+        <v>12741432</v>
+      </c>
+      <c r="H36" t="n">
+        <v>5755589</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="K36" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="L36" t="n">
+        <v>41.79</v>
+      </c>
+      <c r="M36" t="n">
+        <v>45.88</v>
+      </c>
+      <c r="N36" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="O36" t="n">
+        <v>-6.29</v>
+      </c>
+      <c r="P36" t="n">
+        <v>28.36</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>58.67</v>
       </c>
     </row>
   </sheetData>
@@ -11504,7 +11781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q38"/>
+  <dimension ref="A1:Q39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13472,6 +13749,59 @@
       </c>
       <c r="Q38" t="n">
         <v>89.31999999999999</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B39" t="n">
+        <v>432.6</v>
+      </c>
+      <c r="C39" t="n">
+        <v>455.45</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-5.02</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-11.33</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-5</v>
+      </c>
+      <c r="G39" t="n">
+        <v>406386</v>
+      </c>
+      <c r="H39" t="n">
+        <v>397841</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="K39" t="n">
+        <v>44</v>
+      </c>
+      <c r="L39" t="n">
+        <v>346.52</v>
+      </c>
+      <c r="M39" t="n">
+        <v>428.6</v>
+      </c>
+      <c r="N39" t="n">
+        <v>544.3</v>
+      </c>
+      <c r="O39" t="n">
+        <v>-20.52</v>
+      </c>
+      <c r="P39" t="n">
+        <v>240.57</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>79.81999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -13485,7 +13815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q38"/>
+  <dimension ref="A1:Q39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15453,6 +15783,59 @@
       </c>
       <c r="Q38" t="n">
         <v>1.7</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B39" t="n">
+        <v>258</v>
+      </c>
+      <c r="C39" t="n">
+        <v>259.85</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-7.26</v>
+      </c>
+      <c r="G39" t="n">
+        <v>12129366</v>
+      </c>
+      <c r="H39" t="n">
+        <v>11116049</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="K39" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="L39" t="n">
+        <v>303.57</v>
+      </c>
+      <c r="M39" t="n">
+        <v>275.29</v>
+      </c>
+      <c r="N39" t="n">
+        <v>401.99</v>
+      </c>
+      <c r="O39" t="n">
+        <v>-35.82</v>
+      </c>
+      <c r="P39" t="n">
+        <v>255.5</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.98</v>
       </c>
     </row>
   </sheetData>
@@ -15466,7 +15849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q38"/>
+  <dimension ref="A1:Q39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17434,6 +17817,59 @@
       </c>
       <c r="Q38" t="n">
         <v>3.36</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B39" t="n">
+        <v>819.15</v>
+      </c>
+      <c r="C39" t="n">
+        <v>815.35</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-13.78</v>
+      </c>
+      <c r="G39" t="n">
+        <v>434610</v>
+      </c>
+      <c r="H39" t="n">
+        <v>567956</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="K39" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="L39" t="n">
+        <v>946.4</v>
+      </c>
+      <c r="M39" t="n">
+        <v>903.55</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1203.96</v>
+      </c>
+      <c r="O39" t="n">
+        <v>-31.96</v>
+      </c>
+      <c r="P39" t="n">
+        <v>788.84</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>3.84</v>
       </c>
     </row>
   </sheetData>
@@ -17447,7 +17883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q38"/>
+  <dimension ref="A1:Q39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19415,6 +19851,59 @@
       </c>
       <c r="Q38" t="n">
         <v>42.72</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B39" t="n">
+        <v>945</v>
+      </c>
+      <c r="C39" t="n">
+        <v>974.2</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-4.55</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-7.11</v>
+      </c>
+      <c r="G39" t="n">
+        <v>569734</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1528118</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="J39" t="n">
+        <v>-1.38</v>
+      </c>
+      <c r="K39" t="n">
+        <v>33</v>
+      </c>
+      <c r="L39" t="n">
+        <v>935.03</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1030.71</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1117.2</v>
+      </c>
+      <c r="O39" t="n">
+        <v>-15.41</v>
+      </c>
+      <c r="P39" t="n">
+        <v>682.6</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>38.44</v>
       </c>
     </row>
   </sheetData>
@@ -19428,7 +19917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q38"/>
+  <dimension ref="A1:Q39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21396,6 +21885,59 @@
       </c>
       <c r="Q38" t="n">
         <v>48.35</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B39" t="n">
+        <v>64.06999999999999</v>
+      </c>
+      <c r="C39" t="n">
+        <v>65.54000000000001</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-2.24</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-10</v>
+      </c>
+      <c r="G39" t="n">
+        <v>7608189</v>
+      </c>
+      <c r="H39" t="n">
+        <v>9596521</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K39" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="L39" t="n">
+        <v>59.69</v>
+      </c>
+      <c r="M39" t="n">
+        <v>67.84</v>
+      </c>
+      <c r="N39" t="n">
+        <v>72.47</v>
+      </c>
+      <c r="O39" t="n">
+        <v>-11.59</v>
+      </c>
+      <c r="P39" t="n">
+        <v>44.18</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>45.02</v>
       </c>
     </row>
   </sheetData>
@@ -21409,7 +21951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q38"/>
+  <dimension ref="A1:Q39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23377,6 +23919,59 @@
       </c>
       <c r="Q38" t="n">
         <v>28.71</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B39" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="C39" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-8.98</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-1.47</v>
+      </c>
+      <c r="G39" t="n">
+        <v>309218</v>
+      </c>
+      <c r="H39" t="n">
+        <v>934016</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="K39" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="L39" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="M39" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="N39" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="O39" t="n">
+        <v>-40.66</v>
+      </c>
+      <c r="P39" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>28.47</v>
       </c>
     </row>
   </sheetData>
@@ -23390,7 +23985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q38"/>
+  <dimension ref="A1:Q39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25358,6 +25953,59 @@
       </c>
       <c r="Q38" t="n">
         <v>75.54000000000001</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B39" t="n">
+        <v>981.8</v>
+      </c>
+      <c r="C39" t="n">
+        <v>966.3</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="F39" t="n">
+        <v>16.24</v>
+      </c>
+      <c r="G39" t="n">
+        <v>693725</v>
+      </c>
+      <c r="H39" t="n">
+        <v>128509</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="J39" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="K39" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="L39" t="n">
+        <v>764.15</v>
+      </c>
+      <c r="M39" t="n">
+        <v>881.91</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1001.9</v>
+      </c>
+      <c r="O39" t="n">
+        <v>-2.01</v>
+      </c>
+      <c r="P39" t="n">
+        <v>550.47</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>78.36</v>
       </c>
     </row>
   </sheetData>
@@ -25371,7 +26019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26262,6 +26910,29 @@
         <v>-2.88</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B39" t="n">
+        <v>23118.6</v>
+      </c>
+      <c r="C39" t="n">
+        <v>23398.1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-2.78</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-5.12</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/portfolio_tracker.xlsx
+++ b/data/portfolio_tracker.xlsx
@@ -561,7 +561,7 @@
         <v>-20.08</v>
       </c>
       <c r="H3" t="n">
-        <v>312629</v>
+        <v>313267</v>
       </c>
       <c r="I3" t="n">
         <v>216097</v>
@@ -621,7 +621,7 @@
         <v>3.72</v>
       </c>
       <c r="H4" t="n">
-        <v>12227052</v>
+        <v>12229088</v>
       </c>
       <c r="I4" t="n">
         <v>15754423</v>
@@ -648,10 +648,10 @@
         <v>-5.03</v>
       </c>
       <c r="Q4" t="n">
-        <v>29.08</v>
+        <v>29.49</v>
       </c>
       <c r="R4" t="n">
-        <v>63.14</v>
+        <v>60.87</v>
       </c>
     </row>
     <row r="5">
@@ -681,13 +681,13 @@
         <v>-3.91</v>
       </c>
       <c r="H5" t="n">
-        <v>16440881</v>
+        <v>16447266</v>
       </c>
       <c r="I5" t="n">
         <v>14079098</v>
       </c>
       <c r="J5" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="K5" t="n">
         <v>-0.07000000000000001</v>
@@ -741,7 +741,7 @@
         <v>-2.6</v>
       </c>
       <c r="H6" t="n">
-        <v>717250</v>
+        <v>717435</v>
       </c>
       <c r="I6" t="n">
         <v>620084</v>
@@ -801,7 +801,7 @@
         <v>3.08</v>
       </c>
       <c r="H7" t="n">
-        <v>9367018</v>
+        <v>9369954</v>
       </c>
       <c r="I7" t="n">
         <v>28889413</v>
@@ -861,7 +861,7 @@
         <v>6.95</v>
       </c>
       <c r="H8" t="n">
-        <v>508882</v>
+        <v>508885</v>
       </c>
       <c r="I8" t="n">
         <v>875912</v>
@@ -988,7 +988,7 @@
         <v>-12.2</v>
       </c>
       <c r="H11" t="n">
-        <v>1258902</v>
+        <v>1259157</v>
       </c>
       <c r="I11" t="n">
         <v>1144007</v>
@@ -1048,7 +1048,7 @@
         <v>-10.86</v>
       </c>
       <c r="H12" t="n">
-        <v>18592790</v>
+        <v>18593657</v>
       </c>
       <c r="I12" t="n">
         <v>8847058</v>
@@ -1262,22 +1262,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>101.24</v>
+        <v>101.41</v>
       </c>
       <c r="D19" t="n">
-        <v>103.53</v>
+        <v>102.31</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.21</v>
+        <v>-0.88</v>
       </c>
       <c r="F19" t="n">
-        <v>-5.03</v>
+        <v>-2.79</v>
       </c>
       <c r="G19" t="n">
-        <v>6.96</v>
+        <v>6.04</v>
       </c>
       <c r="H19" t="n">
-        <v>-7.11</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="20">
@@ -1292,22 +1292,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4191.4</v>
+        <v>4164.2</v>
       </c>
       <c r="D20" t="n">
-        <v>4186.7</v>
+        <v>4202.3</v>
       </c>
       <c r="E20" t="n">
-        <v>0.11</v>
+        <v>-0.91</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.48</v>
+        <v>-3.63</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.66</v>
+        <v>-5.67</v>
       </c>
       <c r="H20" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="21">
@@ -1322,22 +1322,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>50840.12</v>
+        <v>51118.91</v>
       </c>
       <c r="D21" t="n">
-        <v>50906.05</v>
+        <v>50926.56</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.13</v>
+        <v>0.38</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.99</v>
+        <v>-1.37</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.65</v>
+        <v>-3.66</v>
       </c>
       <c r="H21" t="n">
-        <v>0.59</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="22">
@@ -1352,19 +1352,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>14.45</v>
+        <v>14.46</v>
       </c>
       <c r="D22" t="n">
         <v>13.49</v>
       </c>
       <c r="E22" t="n">
-        <v>7.12</v>
+        <v>7.19</v>
       </c>
       <c r="F22" t="n">
-        <v>13.87</v>
+        <v>13.95</v>
       </c>
       <c r="G22" t="n">
-        <v>25.76</v>
+        <v>25.85</v>
       </c>
     </row>
   </sheetData>
@@ -2579,7 +2579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3792,12 +3792,1282 @@
         <v>-7.11</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B53" t="n">
+        <v>101.41</v>
+      </c>
+      <c r="C53" t="n">
+        <v>102.31</v>
+      </c>
+      <c r="D53" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="E53" t="n">
+        <v>-2.79</v>
+      </c>
+      <c r="F53" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Prev Price</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Today Price</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Change %</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Weekly Ret %</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Monthly Ret %</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Z Score</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B2" t="n">
+        <v>4046.6</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4070.8</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B3" t="n">
+        <v>4046.6</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4070.8</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B4" t="n">
+        <v>4074.5</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4067.6</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4028.8</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4074.5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B6" t="n">
+        <v>4069.1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4036.3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-1.88</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B7" t="n">
+        <v>4173.6</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4034.7</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3.87</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B8" t="n">
+        <v>4101.2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4100.1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.54</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B9" t="n">
+        <v>4090.3</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4049.1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.46</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B10" t="n">
+        <v>4150.4</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4033.7</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3.53</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B11" t="n">
+        <v>4293</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4095.4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="E11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B12" t="n">
+        <v>4242</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4245.8</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="F12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B13" t="n">
+        <v>4397</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4242</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="E13" t="n">
+        <v>8.59</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B14" t="n">
+        <v>4401.4</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4340.7</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="F14" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B15" t="n">
+        <v>4442.2</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4361.8</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="E15" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="F15" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B16" t="n">
+        <v>4496.6</v>
+      </c>
+      <c r="C16" t="n">
+        <v>4383</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="E16" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="F16" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.69</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B17" t="n">
+        <v>4428.5</v>
+      </c>
+      <c r="C17" t="n">
+        <v>4408.9</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F17" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B18" t="n">
+        <v>4446.7</v>
+      </c>
+      <c r="C18" t="n">
+        <v>4363.6</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="F18" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B19" t="n">
+        <v>4460.5</v>
+      </c>
+      <c r="C19" t="n">
+        <v>4380.4</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="F19" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.03</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B20" t="n">
+        <v>4445.3</v>
+      </c>
+      <c r="C20" t="n">
+        <v>4417.8</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="F20" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B21" t="n">
+        <v>4423.4</v>
+      </c>
+      <c r="C21" t="n">
+        <v>4366</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F21" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B22" t="n">
+        <v>4536.8</v>
+      </c>
+      <c r="C22" t="n">
+        <v>4489.4</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="F22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.97</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B23" t="n">
+        <v>4660.3</v>
+      </c>
+      <c r="C23" t="n">
+        <v>4516.3</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="E23" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="F23" t="n">
+        <v>15.17</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2.03</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B24" t="n">
+        <v>4723.3</v>
+      </c>
+      <c r="C24" t="n">
+        <v>4624.1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="E24" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="F24" t="n">
+        <v>16.12</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B25" t="n">
+        <v>4700</v>
+      </c>
+      <c r="C25" t="n">
+        <v>4640.8</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="E25" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="F25" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2.21</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B26" t="n">
+        <v>4673.3</v>
+      </c>
+      <c r="C26" t="n">
+        <v>4638.1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>15.78</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B27" t="n">
+        <v>4657.3</v>
+      </c>
+      <c r="C27" t="n">
+        <v>4598.2</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="F27" t="n">
+        <v>15.43</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B28" t="n">
+        <v>4504.1</v>
+      </c>
+      <c r="C28" t="n">
+        <v>4609.7</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-2.29</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="F28" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B29" t="n">
+        <v>4480.5</v>
+      </c>
+      <c r="C29" t="n">
+        <v>4478.1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-3.45</v>
+      </c>
+      <c r="F29" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B30" t="n">
+        <v>4407.7</v>
+      </c>
+      <c r="C30" t="n">
+        <v>4431.1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-4.97</v>
+      </c>
+      <c r="F30" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.33</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B31" t="n">
+        <v>4434.3</v>
+      </c>
+      <c r="C31" t="n">
+        <v>4348</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-3.56</v>
+      </c>
+      <c r="F31" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B32" t="n">
+        <v>4525.4</v>
+      </c>
+      <c r="C32" t="n">
+        <v>4366.3</v>
+      </c>
+      <c r="D32" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-1.83</v>
+      </c>
+      <c r="F32" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2.41</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B33" t="n">
+        <v>4478.4</v>
+      </c>
+      <c r="C33" t="n">
+        <v>4491.7</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F33" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B34" t="n">
+        <v>4476.6</v>
+      </c>
+      <c r="C34" t="n">
+        <v>4429.8</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="F34" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B35" t="n">
+        <v>4441.3</v>
+      </c>
+      <c r="C35" t="n">
+        <v>4429.8</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B36" t="n">
+        <v>4466.2</v>
+      </c>
+      <c r="C36" t="n">
+        <v>4393.9</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B37" t="n">
+        <v>4405</v>
+      </c>
+      <c r="C37" t="n">
+        <v>4416</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B38" t="n">
+        <v>4426.3</v>
+      </c>
+      <c r="C38" t="n">
+        <v>4364.5</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B39" t="n">
+        <v>4337.1</v>
+      </c>
+      <c r="C39" t="n">
+        <v>4366.2</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B40" t="n">
+        <v>4316.9</v>
+      </c>
+      <c r="C40" t="n">
+        <v>4351.9</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="F40" t="n">
+        <v>-2.71</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B41" t="n">
+        <v>4391.7</v>
+      </c>
+      <c r="C41" t="n">
+        <v>4332.8</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="F41" t="n">
+        <v>-1.83</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B42" t="n">
+        <v>4392.9</v>
+      </c>
+      <c r="C42" t="n">
+        <v>4387.5</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="F42" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-3.79</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B43" t="n">
+        <v>4392.2</v>
+      </c>
+      <c r="C43" t="n">
+        <v>4399.7</v>
+      </c>
+      <c r="D43" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="F43" t="n">
+        <v>-3.37</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B44" t="n">
+        <v>4393</v>
+      </c>
+      <c r="C44" t="n">
+        <v>4424.9</v>
+      </c>
+      <c r="D44" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F44" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B45" t="n">
+        <v>4362.8</v>
+      </c>
+      <c r="C45" t="n">
+        <v>4383.9</v>
+      </c>
+      <c r="D45" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="F45" t="n">
+        <v>-6.79</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B46" t="n">
+        <v>4327.6</v>
+      </c>
+      <c r="C46" t="n">
+        <v>4376.4</v>
+      </c>
+      <c r="D46" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-1.37</v>
+      </c>
+      <c r="F46" t="n">
+        <v>-7.88</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B47" t="n">
+        <v>4280.8</v>
+      </c>
+      <c r="C47" t="n">
+        <v>4318.4</v>
+      </c>
+      <c r="D47" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="F47" t="n">
+        <v>-8.81</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B48" t="n">
+        <v>4314.3</v>
+      </c>
+      <c r="C48" t="n">
+        <v>4298</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E48" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="F48" t="n">
+        <v>-7.29</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B49" t="n">
+        <v>4167.6</v>
+      </c>
+      <c r="C49" t="n">
+        <v>4321.2</v>
+      </c>
+      <c r="D49" t="n">
+        <v>-3.55</v>
+      </c>
+      <c r="E49" t="n">
+        <v>-4.93</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-10.64</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B50" t="n">
+        <v>4184.4</v>
+      </c>
+      <c r="C50" t="n">
+        <v>4321.2</v>
+      </c>
+      <c r="D50" t="n">
+        <v>-3.17</v>
+      </c>
+      <c r="E50" t="n">
+        <v>-4.55</v>
+      </c>
+      <c r="F50" t="n">
+        <v>-10.28</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-6.69</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B51" t="n">
+        <v>4188.4</v>
+      </c>
+      <c r="C51" t="n">
+        <v>4179.7</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-3.01</v>
+      </c>
+      <c r="F51" t="n">
+        <v>-6.54</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B52" t="n">
+        <v>4191.4</v>
+      </c>
+      <c r="C52" t="n">
+        <v>4186.7</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E52" t="n">
+        <v>-2.48</v>
+      </c>
+      <c r="F52" t="n">
+        <v>-4.66</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B53" t="n">
+        <v>4164.2</v>
+      </c>
+      <c r="C53" t="n">
+        <v>4202.3</v>
+      </c>
+      <c r="D53" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="E53" t="n">
+        <v>-3.63</v>
+      </c>
+      <c r="F53" t="n">
+        <v>-5.67</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3848,22 +5118,22 @@
         <v>46227</v>
       </c>
       <c r="B2" t="n">
-        <v>4046.6</v>
+        <v>51711.65</v>
       </c>
       <c r="C2" t="n">
-        <v>4070.8</v>
+        <v>51947.25</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6</v>
+        <v>0.46</v>
       </c>
       <c r="E2" t="n">
-        <v>1.45</v>
+        <v>-0.38</v>
       </c>
       <c r="F2" t="n">
-        <v>2.02</v>
+        <v>0.19</v>
       </c>
       <c r="G2" t="n">
-        <v>0.29</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="3">
@@ -3871,22 +5141,22 @@
         <v>46227</v>
       </c>
       <c r="B3" t="n">
-        <v>4046.6</v>
+        <v>51711.65</v>
       </c>
       <c r="C3" t="n">
-        <v>4070.8</v>
+        <v>51947.25</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6</v>
+        <v>0.46</v>
       </c>
       <c r="E3" t="n">
-        <v>1.45</v>
+        <v>-0.38</v>
       </c>
       <c r="F3" t="n">
-        <v>2.02</v>
+        <v>0.19</v>
       </c>
       <c r="G3" t="n">
-        <v>0.29</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="4">
@@ -3894,22 +5164,22 @@
         <v>46230</v>
       </c>
       <c r="B4" t="n">
-        <v>4074.5</v>
+        <v>52210.08</v>
       </c>
       <c r="C4" t="n">
-        <v>4067.6</v>
+        <v>51947.25</v>
       </c>
       <c r="D4" t="n">
-        <v>0.17</v>
+        <v>0.51</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6</v>
+        <v>0.72</v>
       </c>
       <c r="F4" t="n">
-        <v>1.09</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>0.93</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="5">
@@ -3917,22 +5187,22 @@
         <v>46231</v>
       </c>
       <c r="B5" t="n">
-        <v>4028.8</v>
+        <v>52747.32</v>
       </c>
       <c r="C5" t="n">
-        <v>4074.5</v>
+        <v>52210.08</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.12</v>
+        <v>1.03</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.04</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.22</v>
+        <v>1.68</v>
       </c>
       <c r="G5" t="n">
-        <v>0.39</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="6">
@@ -3940,22 +5210,22 @@
         <v>46232</v>
       </c>
       <c r="B6" t="n">
-        <v>4069.1</v>
+        <v>51818.64</v>
       </c>
       <c r="C6" t="n">
-        <v>4036.3</v>
+        <v>52747.32</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8100000000000001</v>
+        <v>-1.76</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.88</v>
+        <v>-0.77</v>
       </c>
       <c r="F6" t="n">
-        <v>1.16</v>
+        <v>-0.7</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.65</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="7">
@@ -3963,22 +5233,22 @@
         <v>46233</v>
       </c>
       <c r="B7" t="n">
-        <v>4173.6</v>
+        <v>52006.44</v>
       </c>
       <c r="C7" t="n">
-        <v>4034.7</v>
+        <v>51594.14</v>
       </c>
       <c r="D7" t="n">
-        <v>3.44</v>
+        <v>0.8</v>
       </c>
       <c r="E7" t="n">
-        <v>3.14</v>
+        <v>0.57</v>
       </c>
       <c r="F7" t="n">
-        <v>3.75</v>
+        <v>-0.6</v>
       </c>
       <c r="G7" t="n">
-        <v>3.87</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="8">
@@ -3986,22 +5256,22 @@
         <v>46234</v>
       </c>
       <c r="B8" t="n">
-        <v>4101.2</v>
+        <v>52407.88</v>
       </c>
       <c r="C8" t="n">
-        <v>4100.1</v>
+        <v>52208.06</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03</v>
+        <v>0.38</v>
       </c>
       <c r="E8" t="n">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="G8" t="n">
-        <v>2.54</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="9">
@@ -4009,22 +5279,22 @@
         <v>46237</v>
       </c>
       <c r="B9" t="n">
-        <v>4090.3</v>
+        <v>52996.27</v>
       </c>
       <c r="C9" t="n">
-        <v>4049.1</v>
+        <v>52485.03</v>
       </c>
       <c r="D9" t="n">
-        <v>1.02</v>
+        <v>0.97</v>
       </c>
       <c r="E9" t="n">
-        <v>0.39</v>
+        <v>1.51</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.54</v>
+        <v>0.18</v>
       </c>
       <c r="G9" t="n">
-        <v>3.46</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="10">
@@ -4032,22 +5302,22 @@
         <v>46238</v>
       </c>
       <c r="B10" t="n">
-        <v>4150.4</v>
+        <v>54173.91</v>
       </c>
       <c r="C10" t="n">
-        <v>4033.7</v>
+        <v>53178.41</v>
       </c>
       <c r="D10" t="n">
-        <v>2.89</v>
+        <v>1.87</v>
       </c>
       <c r="E10" t="n">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.11</v>
+        <v>2.11</v>
       </c>
       <c r="G10" t="n">
-        <v>3.53</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="11">
@@ -4055,22 +5325,22 @@
         <v>46239</v>
       </c>
       <c r="B11" t="n">
-        <v>4293</v>
+        <v>54544.79</v>
       </c>
       <c r="C11" t="n">
-        <v>4095.4</v>
+        <v>54085.88</v>
       </c>
       <c r="D11" t="n">
-        <v>4.82</v>
+        <v>0.85</v>
       </c>
       <c r="E11" t="n">
-        <v>6.4</v>
+        <v>5.72</v>
       </c>
       <c r="F11" t="n">
-        <v>3.56</v>
+        <v>3.06</v>
       </c>
       <c r="G11" t="n">
-        <v>1.78</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -4078,22 +5348,22 @@
         <v>46240</v>
       </c>
       <c r="B12" t="n">
-        <v>4242</v>
+        <v>53885.1</v>
       </c>
       <c r="C12" t="n">
-        <v>4245.8</v>
+        <v>54349.12</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.09</v>
+        <v>-0.85</v>
       </c>
       <c r="E12" t="n">
-        <v>3.46</v>
+        <v>3.21</v>
       </c>
       <c r="F12" t="n">
-        <v>4.2</v>
+        <v>2.94</v>
       </c>
       <c r="G12" t="n">
-        <v>2.23</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="13">
@@ -4101,22 +5371,22 @@
         <v>46241</v>
       </c>
       <c r="B13" t="n">
-        <v>4397</v>
+        <v>53987.31</v>
       </c>
       <c r="C13" t="n">
-        <v>4242</v>
+        <v>53885.1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.65</v>
+        <v>0.19</v>
       </c>
       <c r="E13" t="n">
-        <v>8.59</v>
+        <v>2.86</v>
       </c>
       <c r="F13" t="n">
-        <v>6.45</v>
+        <v>2.86</v>
       </c>
       <c r="G13" t="n">
-        <v>2.2</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="14">
@@ -4124,22 +5394,22 @@
         <v>46244</v>
       </c>
       <c r="B14" t="n">
-        <v>4401.4</v>
+        <v>53969.28</v>
       </c>
       <c r="C14" t="n">
-        <v>4340.7</v>
+        <v>54036.93</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4</v>
+        <v>-0.13</v>
       </c>
       <c r="E14" t="n">
-        <v>9.119999999999999</v>
+        <v>1.49</v>
       </c>
       <c r="F14" t="n">
-        <v>7.24</v>
+        <v>2.53</v>
       </c>
       <c r="G14" t="n">
-        <v>2.2</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="15">
@@ -4147,22 +5417,22 @@
         <v>46245</v>
       </c>
       <c r="B15" t="n">
-        <v>4442.2</v>
+        <v>54016.06</v>
       </c>
       <c r="C15" t="n">
-        <v>4361.8</v>
+        <v>53975.98</v>
       </c>
       <c r="D15" t="n">
-        <v>1.84</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>8.470000000000001</v>
+        <v>-0.13</v>
       </c>
       <c r="F15" t="n">
-        <v>11.14</v>
+        <v>2.89</v>
       </c>
       <c r="G15" t="n">
-        <v>3.22</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="16">
@@ -4170,22 +5440,22 @@
         <v>46246</v>
       </c>
       <c r="B16" t="n">
-        <v>4496.6</v>
+        <v>53795.51</v>
       </c>
       <c r="C16" t="n">
-        <v>4383</v>
+        <v>53791.85</v>
       </c>
       <c r="D16" t="n">
-        <v>2.59</v>
+        <v>0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>5.91</v>
+        <v>-1.02</v>
       </c>
       <c r="F16" t="n">
-        <v>10.72</v>
+        <v>2.45</v>
       </c>
       <c r="G16" t="n">
-        <v>1.69</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="17">
@@ -4193,22 +5463,22 @@
         <v>46247</v>
       </c>
       <c r="B17" t="n">
-        <v>4428.5</v>
+        <v>53964.83</v>
       </c>
       <c r="C17" t="n">
-        <v>4408.9</v>
+        <v>53770.27</v>
       </c>
       <c r="D17" t="n">
-        <v>0.44</v>
+        <v>0.36</v>
       </c>
       <c r="E17" t="n">
-        <v>4.4</v>
+        <v>0.15</v>
       </c>
       <c r="F17" t="n">
-        <v>9.51</v>
+        <v>2.52</v>
       </c>
       <c r="G17" t="n">
-        <v>2.16</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="18">
@@ -4216,45 +5486,30 @@
         <v>46248</v>
       </c>
       <c r="B18" t="n">
-        <v>4446.7</v>
+        <v>53804.83</v>
       </c>
       <c r="C18" t="n">
-        <v>4363.6</v>
+        <v>53839.99</v>
       </c>
       <c r="D18" t="n">
-        <v>1.9</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>2.44</v>
+        <v>-0.43</v>
       </c>
       <c r="F18" t="n">
-        <v>11.57</v>
+        <v>2.49</v>
       </c>
       <c r="G18" t="n">
-        <v>1.65</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
         <v>46251</v>
       </c>
-      <c r="B19" t="n">
-        <v>4460.5</v>
-      </c>
       <c r="C19" t="n">
-        <v>4380.4</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="E19" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="F19" t="n">
-        <v>11.16</v>
-      </c>
-      <c r="G19" t="n">
-        <v>2.03</v>
+        <v>53732.41</v>
       </c>
     </row>
     <row r="20">
@@ -4262,22 +5517,22 @@
         <v>46252</v>
       </c>
       <c r="B20" t="n">
-        <v>4445.3</v>
+        <v>53343.4</v>
       </c>
       <c r="C20" t="n">
-        <v>4417.8</v>
+        <v>53459.78</v>
       </c>
       <c r="D20" t="n">
-        <v>0.62</v>
+        <v>-0.22</v>
       </c>
       <c r="E20" t="n">
-        <v>1.42</v>
+        <v>-0.83</v>
       </c>
       <c r="F20" t="n">
-        <v>10.85</v>
+        <v>2.9</v>
       </c>
       <c r="G20" t="n">
-        <v>1.91</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="21">
@@ -4285,22 +5540,22 @@
         <v>46253</v>
       </c>
       <c r="B21" t="n">
-        <v>4423.4</v>
+        <v>53463.05</v>
       </c>
       <c r="C21" t="n">
-        <v>4366</v>
+        <v>53343.4</v>
       </c>
       <c r="D21" t="n">
-        <v>1.31</v>
+        <v>0.22</v>
       </c>
       <c r="E21" t="n">
-        <v>0.33</v>
+        <v>-0.57</v>
       </c>
       <c r="F21" t="n">
-        <v>8.65</v>
+        <v>2.37</v>
       </c>
       <c r="G21" t="n">
-        <v>0.89</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="22">
@@ -4308,22 +5563,22 @@
         <v>46254</v>
       </c>
       <c r="B22" t="n">
-        <v>4536.8</v>
+        <v>52759.21</v>
       </c>
       <c r="C22" t="n">
-        <v>4489.4</v>
+        <v>53463.05</v>
       </c>
       <c r="D22" t="n">
-        <v>1.06</v>
+        <v>-1.32</v>
       </c>
       <c r="E22" t="n">
-        <v>3.97</v>
+        <v>-2.01</v>
       </c>
       <c r="F22" t="n">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="G22" t="n">
-        <v>2.97</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="23">
@@ -4331,22 +5586,22 @@
         <v>46255</v>
       </c>
       <c r="B23" t="n">
-        <v>4660.3</v>
+        <v>53277.01</v>
       </c>
       <c r="C23" t="n">
-        <v>4516.3</v>
+        <v>52759.21</v>
       </c>
       <c r="D23" t="n">
-        <v>3.19</v>
+        <v>0.98</v>
       </c>
       <c r="E23" t="n">
-        <v>6.39</v>
+        <v>-0.85</v>
       </c>
       <c r="F23" t="n">
-        <v>15.17</v>
+        <v>3.03</v>
       </c>
       <c r="G23" t="n">
-        <v>2.03</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="24">
@@ -4354,22 +5609,22 @@
         <v>46258</v>
       </c>
       <c r="B24" t="n">
-        <v>4723.3</v>
+        <v>53417.16</v>
       </c>
       <c r="C24" t="n">
-        <v>4624.1</v>
+        <v>53277.01</v>
       </c>
       <c r="D24" t="n">
-        <v>2.15</v>
+        <v>0.26</v>
       </c>
       <c r="E24" t="n">
-        <v>6.92</v>
+        <v>-0.08</v>
       </c>
       <c r="F24" t="n">
-        <v>16.12</v>
+        <v>2.83</v>
       </c>
       <c r="G24" t="n">
-        <v>1.57</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="25">
@@ -4377,22 +5632,22 @@
         <v>46259</v>
       </c>
       <c r="B25" t="n">
-        <v>4700</v>
+        <v>53577.4</v>
       </c>
       <c r="C25" t="n">
-        <v>4640.8</v>
+        <v>53417.16</v>
       </c>
       <c r="D25" t="n">
-        <v>1.28</v>
+        <v>0.3</v>
       </c>
       <c r="E25" t="n">
-        <v>7.65</v>
+        <v>0.44</v>
       </c>
       <c r="F25" t="n">
-        <v>15.35</v>
+        <v>2.62</v>
       </c>
       <c r="G25" t="n">
-        <v>2.21</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="26">
@@ -4400,22 +5655,22 @@
         <v>46260</v>
       </c>
       <c r="B26" t="n">
-        <v>4673.3</v>
+        <v>53463.88</v>
       </c>
       <c r="C26" t="n">
-        <v>4638.1</v>
+        <v>53577.4</v>
       </c>
       <c r="D26" t="n">
-        <v>0.76</v>
+        <v>-0.21</v>
       </c>
       <c r="E26" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>15.78</v>
+        <v>1.36</v>
       </c>
       <c r="G26" t="n">
-        <v>2.8</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="27">
@@ -4423,22 +5678,22 @@
         <v>46261</v>
       </c>
       <c r="B27" t="n">
-        <v>4657.3</v>
+        <v>53569.44</v>
       </c>
       <c r="C27" t="n">
-        <v>4598.2</v>
+        <v>53463.88</v>
       </c>
       <c r="D27" t="n">
-        <v>1.29</v>
+        <v>0.2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.12</v>
+        <v>1.54</v>
       </c>
       <c r="F27" t="n">
-        <v>15.43</v>
+        <v>3.83</v>
       </c>
       <c r="G27" t="n">
-        <v>1.88</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="28">
@@ -4446,22 +5701,22 @@
         <v>46262</v>
       </c>
       <c r="B28" t="n">
-        <v>4504.1</v>
+        <v>53559.99</v>
       </c>
       <c r="C28" t="n">
-        <v>4609.7</v>
+        <v>53569.44</v>
       </c>
       <c r="D28" t="n">
-        <v>-2.29</v>
+        <v>-0.02</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.6</v>
+        <v>0.53</v>
       </c>
       <c r="F28" t="n">
-        <v>9.85</v>
+        <v>2.59</v>
       </c>
       <c r="G28" t="n">
-        <v>1.7</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="29">
@@ -4469,22 +5724,22 @@
         <v>46265</v>
       </c>
       <c r="B29" t="n">
-        <v>4480.5</v>
+        <v>53212.7</v>
       </c>
       <c r="C29" t="n">
-        <v>4478.1</v>
+        <v>53559.99</v>
       </c>
       <c r="D29" t="n">
-        <v>0.05</v>
+        <v>-0.65</v>
       </c>
       <c r="E29" t="n">
-        <v>-3.45</v>
+        <v>-0.38</v>
       </c>
       <c r="F29" t="n">
-        <v>10.65</v>
+        <v>1.39</v>
       </c>
       <c r="G29" t="n">
-        <v>0.19</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="30">
@@ -4492,22 +5747,22 @@
         <v>46266</v>
       </c>
       <c r="B30" t="n">
-        <v>4407.7</v>
+        <v>52960.85</v>
       </c>
       <c r="C30" t="n">
-        <v>4431.1</v>
+        <v>53185.9</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.53</v>
+        <v>-0.42</v>
       </c>
       <c r="E30" t="n">
-        <v>-4.97</v>
+        <v>-0.85</v>
       </c>
       <c r="F30" t="n">
-        <v>9.27</v>
+        <v>0.91</v>
       </c>
       <c r="G30" t="n">
-        <v>2.33</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="31">
@@ -4515,22 +5770,22 @@
         <v>46267</v>
       </c>
       <c r="B31" t="n">
-        <v>4434.3</v>
+        <v>53171.82</v>
       </c>
       <c r="C31" t="n">
-        <v>4348</v>
+        <v>52766.88</v>
       </c>
       <c r="D31" t="n">
-        <v>1.98</v>
+        <v>0.77</v>
       </c>
       <c r="E31" t="n">
-        <v>-3.56</v>
+        <v>-0.55</v>
       </c>
       <c r="F31" t="n">
-        <v>8.279999999999999</v>
+        <v>-1.69</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="32">
@@ -4538,22 +5793,22 @@
         <v>46268</v>
       </c>
       <c r="B32" t="n">
-        <v>4525.4</v>
+        <v>53412.4</v>
       </c>
       <c r="C32" t="n">
-        <v>4366.3</v>
+        <v>53061.95</v>
       </c>
       <c r="D32" t="n">
-        <v>3.64</v>
+        <v>0.66</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.83</v>
+        <v>-0.1</v>
       </c>
       <c r="F32" t="n">
-        <v>6.59</v>
+        <v>-1.25</v>
       </c>
       <c r="G32" t="n">
-        <v>2.41</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="33">
@@ -4561,1215 +5816,6 @@
         <v>46269</v>
       </c>
       <c r="B33" t="n">
-        <v>4478.4</v>
-      </c>
-      <c r="C33" t="n">
-        <v>4491.7</v>
-      </c>
-      <c r="D33" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="F33" t="n">
-        <v>5.57</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>46272</v>
-      </c>
-      <c r="B34" t="n">
-        <v>4476.6</v>
-      </c>
-      <c r="C34" t="n">
-        <v>4429.8</v>
-      </c>
-      <c r="D34" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="E34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="F34" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="G34" t="n">
-        <v>1.14</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>46273</v>
-      </c>
-      <c r="B35" t="n">
-        <v>4441.3</v>
-      </c>
-      <c r="C35" t="n">
-        <v>4429.8</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="F35" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="G35" t="n">
-        <v>1.14</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>46274</v>
-      </c>
-      <c r="B36" t="n">
-        <v>4466.2</v>
-      </c>
-      <c r="C36" t="n">
-        <v>4393.9</v>
-      </c>
-      <c r="D36" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="E36" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="F36" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>46275</v>
-      </c>
-      <c r="B37" t="n">
-        <v>4405</v>
-      </c>
-      <c r="C37" t="n">
-        <v>4416</v>
-      </c>
-      <c r="D37" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G37" t="n">
-        <v>1.04</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>46276</v>
-      </c>
-      <c r="B38" t="n">
-        <v>4426.3</v>
-      </c>
-      <c r="C38" t="n">
-        <v>4364.5</v>
-      </c>
-      <c r="D38" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="E38" t="n">
-        <v>-1.46</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="G38" t="n">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="B39" t="n">
-        <v>4337.1</v>
-      </c>
-      <c r="C39" t="n">
-        <v>4366.2</v>
-      </c>
-      <c r="D39" t="n">
-        <v>-0.67</v>
-      </c>
-      <c r="E39" t="n">
-        <v>-2.09</v>
-      </c>
-      <c r="F39" t="n">
-        <v>-0.61</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="B40" t="n">
-        <v>4316.9</v>
-      </c>
-      <c r="C40" t="n">
-        <v>4351.9</v>
-      </c>
-      <c r="D40" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="E40" t="n">
-        <v>-2.75</v>
-      </c>
-      <c r="F40" t="n">
-        <v>-2.71</v>
-      </c>
-      <c r="G40" t="n">
-        <v>-0.51</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="B41" t="n">
-        <v>4391.7</v>
-      </c>
-      <c r="C41" t="n">
-        <v>4332.8</v>
-      </c>
-      <c r="D41" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="E41" t="n">
-        <v>-1.55</v>
-      </c>
-      <c r="F41" t="n">
-        <v>-1.83</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="B42" t="n">
-        <v>4392.9</v>
-      </c>
-      <c r="C42" t="n">
-        <v>4387.5</v>
-      </c>
-      <c r="D42" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E42" t="n">
-        <v>-0.33</v>
-      </c>
-      <c r="F42" t="n">
-        <v>-0.63</v>
-      </c>
-      <c r="G42" t="n">
-        <v>-3.79</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="B43" t="n">
-        <v>4392.2</v>
-      </c>
-      <c r="C43" t="n">
-        <v>4399.7</v>
-      </c>
-      <c r="D43" t="n">
-        <v>-0.17</v>
-      </c>
-      <c r="E43" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="F43" t="n">
-        <v>-3.37</v>
-      </c>
-      <c r="G43" t="n">
-        <v>-0.63</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B44" t="n">
-        <v>4393</v>
-      </c>
-      <c r="C44" t="n">
-        <v>4424.9</v>
-      </c>
-      <c r="D44" t="n">
-        <v>-0.72</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="F44" t="n">
-        <v>-3.9</v>
-      </c>
-      <c r="G44" t="n">
-        <v>-0.44</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="n">
-        <v>46287</v>
-      </c>
-      <c r="B45" t="n">
-        <v>4362.8</v>
-      </c>
-      <c r="C45" t="n">
-        <v>4383.9</v>
-      </c>
-      <c r="D45" t="n">
-        <v>-0.48</v>
-      </c>
-      <c r="E45" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="F45" t="n">
-        <v>-6.79</v>
-      </c>
-      <c r="G45" t="n">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="B46" t="n">
-        <v>4327.6</v>
-      </c>
-      <c r="C46" t="n">
-        <v>4376.4</v>
-      </c>
-      <c r="D46" t="n">
-        <v>-1.12</v>
-      </c>
-      <c r="E46" t="n">
-        <v>-1.37</v>
-      </c>
-      <c r="F46" t="n">
-        <v>-7.88</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="B47" t="n">
-        <v>4280.8</v>
-      </c>
-      <c r="C47" t="n">
-        <v>4318.4</v>
-      </c>
-      <c r="D47" t="n">
-        <v>-0.87</v>
-      </c>
-      <c r="E47" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="F47" t="n">
-        <v>-8.81</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="B48" t="n">
-        <v>4314.3</v>
-      </c>
-      <c r="C48" t="n">
-        <v>4298</v>
-      </c>
-      <c r="D48" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E48" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="F48" t="n">
-        <v>-7.29</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B49" t="n">
-        <v>4167.6</v>
-      </c>
-      <c r="C49" t="n">
-        <v>4321.2</v>
-      </c>
-      <c r="D49" t="n">
-        <v>-3.55</v>
-      </c>
-      <c r="E49" t="n">
-        <v>-4.93</v>
-      </c>
-      <c r="F49" t="n">
-        <v>-10.64</v>
-      </c>
-      <c r="G49" t="n">
-        <v>-0.24</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="B50" t="n">
-        <v>4184.4</v>
-      </c>
-      <c r="C50" t="n">
-        <v>4321.2</v>
-      </c>
-      <c r="D50" t="n">
-        <v>-3.17</v>
-      </c>
-      <c r="E50" t="n">
-        <v>-4.55</v>
-      </c>
-      <c r="F50" t="n">
-        <v>-10.28</v>
-      </c>
-      <c r="G50" t="n">
-        <v>-6.69</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B51" t="n">
-        <v>4188.4</v>
-      </c>
-      <c r="C51" t="n">
-        <v>4179.7</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E51" t="n">
-        <v>-3.01</v>
-      </c>
-      <c r="F51" t="n">
-        <v>-6.54</v>
-      </c>
-      <c r="G51" t="n">
-        <v>1.49</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="B52" t="n">
-        <v>4191.4</v>
-      </c>
-      <c r="C52" t="n">
-        <v>4186.7</v>
-      </c>
-      <c r="D52" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E52" t="n">
-        <v>-2.48</v>
-      </c>
-      <c r="F52" t="n">
-        <v>-4.66</v>
-      </c>
-      <c r="G52" t="n">
-        <v>0.13</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G51"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Prev Price</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Today Price</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Change %</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Weekly Ret %</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Monthly Ret %</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Z Score</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>46227</v>
-      </c>
-      <c r="B2" t="n">
-        <v>51711.65</v>
-      </c>
-      <c r="C2" t="n">
-        <v>51947.25</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>46227</v>
-      </c>
-      <c r="B3" t="n">
-        <v>51711.65</v>
-      </c>
-      <c r="C3" t="n">
-        <v>51947.25</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>46230</v>
-      </c>
-      <c r="B4" t="n">
-        <v>52210.08</v>
-      </c>
-      <c r="C4" t="n">
-        <v>51947.25</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>46231</v>
-      </c>
-      <c r="B5" t="n">
-        <v>52747.32</v>
-      </c>
-      <c r="C5" t="n">
-        <v>52210.08</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>46232</v>
-      </c>
-      <c r="B6" t="n">
-        <v>51818.64</v>
-      </c>
-      <c r="C6" t="n">
-        <v>52747.32</v>
-      </c>
-      <c r="D6" t="n">
-        <v>-1.76</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="F6" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-0.37</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>46233</v>
-      </c>
-      <c r="B7" t="n">
-        <v>52006.44</v>
-      </c>
-      <c r="C7" t="n">
-        <v>51594.14</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2.64</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="B8" t="n">
-        <v>52407.88</v>
-      </c>
-      <c r="C8" t="n">
-        <v>52208.06</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>46237</v>
-      </c>
-      <c r="B9" t="n">
-        <v>52996.27</v>
-      </c>
-      <c r="C9" t="n">
-        <v>52485.03</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.19</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="B10" t="n">
-        <v>54173.91</v>
-      </c>
-      <c r="C10" t="n">
-        <v>53178.41</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="E10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="F10" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1.93</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>46239</v>
-      </c>
-      <c r="B11" t="n">
-        <v>54544.79</v>
-      </c>
-      <c r="C11" t="n">
-        <v>54085.88</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="E11" t="n">
-        <v>5.72</v>
-      </c>
-      <c r="F11" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>46240</v>
-      </c>
-      <c r="B12" t="n">
-        <v>53885.1</v>
-      </c>
-      <c r="C12" t="n">
-        <v>54349.12</v>
-      </c>
-      <c r="D12" t="n">
-        <v>-0.85</v>
-      </c>
-      <c r="E12" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="F12" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>46241</v>
-      </c>
-      <c r="B13" t="n">
-        <v>53987.31</v>
-      </c>
-      <c r="C13" t="n">
-        <v>53885.1</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E13" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="G13" t="n">
-        <v>-0.14</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>46244</v>
-      </c>
-      <c r="B14" t="n">
-        <v>53969.28</v>
-      </c>
-      <c r="C14" t="n">
-        <v>54036.93</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="F14" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.14</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>46245</v>
-      </c>
-      <c r="B15" t="n">
-        <v>54016.06</v>
-      </c>
-      <c r="C15" t="n">
-        <v>53975.98</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E15" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="F15" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>46246</v>
-      </c>
-      <c r="B16" t="n">
-        <v>53795.51</v>
-      </c>
-      <c r="C16" t="n">
-        <v>53791.85</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E16" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="F16" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>46247</v>
-      </c>
-      <c r="B17" t="n">
-        <v>53964.83</v>
-      </c>
-      <c r="C17" t="n">
-        <v>53770.27</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="F17" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>46248</v>
-      </c>
-      <c r="B18" t="n">
-        <v>53804.83</v>
-      </c>
-      <c r="C18" t="n">
-        <v>53839.99</v>
-      </c>
-      <c r="D18" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="E18" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="F18" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>46251</v>
-      </c>
-      <c r="C19" t="n">
-        <v>53732.41</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>46252</v>
-      </c>
-      <c r="B20" t="n">
-        <v>53343.4</v>
-      </c>
-      <c r="C20" t="n">
-        <v>53459.78</v>
-      </c>
-      <c r="D20" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="E20" t="n">
-        <v>-0.83</v>
-      </c>
-      <c r="F20" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="G20" t="n">
-        <v>-0.49</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>46253</v>
-      </c>
-      <c r="B21" t="n">
-        <v>53463.05</v>
-      </c>
-      <c r="C21" t="n">
-        <v>53343.4</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E21" t="n">
-        <v>-0.57</v>
-      </c>
-      <c r="F21" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>46254</v>
-      </c>
-      <c r="B22" t="n">
-        <v>52759.21</v>
-      </c>
-      <c r="C22" t="n">
-        <v>53463.05</v>
-      </c>
-      <c r="D22" t="n">
-        <v>-1.32</v>
-      </c>
-      <c r="E22" t="n">
-        <v>-2.01</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="G22" t="n">
-        <v>-0.38</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>46255</v>
-      </c>
-      <c r="B23" t="n">
-        <v>53277.01</v>
-      </c>
-      <c r="C23" t="n">
-        <v>52759.21</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="E23" t="n">
-        <v>-0.85</v>
-      </c>
-      <c r="F23" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>46258</v>
-      </c>
-      <c r="B24" t="n">
-        <v>53417.16</v>
-      </c>
-      <c r="C24" t="n">
-        <v>53277.01</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E24" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="F24" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="G24" t="n">
-        <v>-0.08</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>46259</v>
-      </c>
-      <c r="B25" t="n">
-        <v>53577.4</v>
-      </c>
-      <c r="C25" t="n">
-        <v>53417.16</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="F25" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>46260</v>
-      </c>
-      <c r="B26" t="n">
-        <v>53463.88</v>
-      </c>
-      <c r="C26" t="n">
-        <v>53577.4</v>
-      </c>
-      <c r="D26" t="n">
-        <v>-0.21</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="G26" t="n">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>46261</v>
-      </c>
-      <c r="B27" t="n">
-        <v>53569.44</v>
-      </c>
-      <c r="C27" t="n">
-        <v>53463.88</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E27" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="F27" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.87</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>46262</v>
-      </c>
-      <c r="B28" t="n">
-        <v>53559.99</v>
-      </c>
-      <c r="C28" t="n">
-        <v>53569.44</v>
-      </c>
-      <c r="D28" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="F28" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="B29" t="n">
-        <v>53212.7</v>
-      </c>
-      <c r="C29" t="n">
-        <v>53559.99</v>
-      </c>
-      <c r="D29" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="E29" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="F29" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="G29" t="n">
-        <v>-0.71</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B30" t="n">
-        <v>52960.85</v>
-      </c>
-      <c r="C30" t="n">
-        <v>53185.9</v>
-      </c>
-      <c r="D30" t="n">
-        <v>-0.42</v>
-      </c>
-      <c r="E30" t="n">
-        <v>-0.85</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="G30" t="n">
-        <v>-0.73</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>46267</v>
-      </c>
-      <c r="B31" t="n">
-        <v>53171.82</v>
-      </c>
-      <c r="C31" t="n">
-        <v>52766.88</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E31" t="n">
-        <v>-0.55</v>
-      </c>
-      <c r="F31" t="n">
-        <v>-1.69</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0.71</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>46268</v>
-      </c>
-      <c r="B32" t="n">
-        <v>53412.4</v>
-      </c>
-      <c r="C32" t="n">
-        <v>53061.95</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="E32" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="F32" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="G32" t="n">
-        <v>2.74</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="n">
-        <v>46269</v>
-      </c>
-      <c r="B33" t="n">
         <v>53409.5</v>
       </c>
       <c r="C33" t="n">
@@ -6200,6 +6246,29 @@
       </c>
       <c r="G51" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B52" t="n">
+        <v>51118.91</v>
+      </c>
+      <c r="C52" t="n">
+        <v>50926.56</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E52" t="n">
+        <v>-1.37</v>
+      </c>
+      <c r="F52" t="n">
+        <v>-3.66</v>
+      </c>
+      <c r="G52" t="n">
+        <v>1.81</v>
       </c>
     </row>
   </sheetData>

--- a/data/portfolio_tracker.xlsx
+++ b/data/portfolio_tracker.xlsx
@@ -621,7 +621,7 @@
         <v>18.27</v>
       </c>
       <c r="H4" t="n">
-        <v>58610045</v>
+        <v>58610367</v>
       </c>
       <c r="I4" t="n">
         <v>36758983</v>
@@ -681,7 +681,7 @@
         <v>-2.03</v>
       </c>
       <c r="H5" t="n">
-        <v>11522059</v>
+        <v>11528925</v>
       </c>
       <c r="I5" t="n">
         <v>12994056</v>
@@ -741,7 +741,7 @@
         <v>-2.13</v>
       </c>
       <c r="H6" t="n">
-        <v>768048</v>
+        <v>768065</v>
       </c>
       <c r="I6" t="n">
         <v>497871</v>
@@ -801,7 +801,7 @@
         <v>-1.2</v>
       </c>
       <c r="H7" t="n">
-        <v>20973399</v>
+        <v>20990086</v>
       </c>
       <c r="I7" t="n">
         <v>50282886</v>
@@ -861,7 +861,7 @@
         <v>-9.460000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>258567</v>
+        <v>258582</v>
       </c>
       <c r="I8" t="n">
         <v>253869</v>
@@ -988,7 +988,7 @@
         <v>2.16</v>
       </c>
       <c r="H11" t="n">
-        <v>1560984</v>
+        <v>1561240</v>
       </c>
       <c r="I11" t="n">
         <v>1042636</v>
@@ -1048,7 +1048,7 @@
         <v>-9.289999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>18511754</v>
+        <v>18514146</v>
       </c>
       <c r="I12" t="n">
         <v>8538586</v>
@@ -1262,22 +1262,22 @@
         </is>
       </c>
       <c r="C19" t="n">
+        <v>106.85</v>
+      </c>
+      <c r="D19" t="n">
         <v>109.55</v>
       </c>
-      <c r="D19" t="n">
-        <v>109.86</v>
-      </c>
       <c r="E19" t="n">
+        <v>-2.46</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="H19" t="n">
         <v>-0.28</v>
-      </c>
-      <c r="F19" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="G19" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.25</v>
       </c>
     </row>
     <row r="20">
@@ -1292,22 +1292,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4159.7</v>
+        <v>4161</v>
       </c>
       <c r="D20" t="n">
-        <v>4181.1</v>
+        <v>4160.1</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.51</v>
+        <v>0.02</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.74</v>
+        <v>-0.39</v>
       </c>
       <c r="G20" t="n">
-        <v>-5.99</v>
+        <v>-5.08</v>
       </c>
       <c r="H20" t="n">
-        <v>0.32</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="21">
@@ -1322,22 +1322,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>52000.48</v>
+        <v>52472.73</v>
       </c>
       <c r="D21" t="n">
-        <v>52002.41</v>
+        <v>51966.03</v>
       </c>
       <c r="E21" t="n">
-        <v>-0</v>
+        <v>0.98</v>
       </c>
       <c r="F21" t="n">
-        <v>0.29</v>
+        <v>1.55</v>
       </c>
       <c r="G21" t="n">
-        <v>0.61</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.16</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="22">
@@ -1365,9 +1365,6 @@
       </c>
       <c r="G22" t="n">
         <v>20.18</v>
-      </c>
-      <c r="H22" t="n">
-        <v/>
       </c>
     </row>
   </sheetData>
@@ -2835,7 +2832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4324,12 +4321,1558 @@
         <v>0.25</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B65" t="n">
+        <v>106.85</v>
+      </c>
+      <c r="C65" t="n">
+        <v>109.55</v>
+      </c>
+      <c r="D65" t="n">
+        <v>-2.46</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F65" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G65" t="n">
+        <v>-0.28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G65"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Prev Price</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Today Price</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Change %</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Weekly Ret %</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Monthly Ret %</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Z Score</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B2" t="n">
+        <v>4046.6</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4070.8</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B3" t="n">
+        <v>4046.6</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4070.8</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B4" t="n">
+        <v>4074.5</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4067.6</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4028.8</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4074.5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B6" t="n">
+        <v>4069.1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4036.3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-1.88</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B7" t="n">
+        <v>4173.6</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4034.7</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3.87</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B8" t="n">
+        <v>4101.2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4100.1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.54</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B9" t="n">
+        <v>4090.3</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4049.1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.46</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B10" t="n">
+        <v>4150.4</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4033.7</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3.53</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B11" t="n">
+        <v>4293</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4095.4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="E11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B12" t="n">
+        <v>4242</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4245.8</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="F12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B13" t="n">
+        <v>4397</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4242</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="E13" t="n">
+        <v>8.59</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B14" t="n">
+        <v>4401.4</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4340.7</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="F14" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B15" t="n">
+        <v>4442.2</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4361.8</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="E15" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="F15" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B16" t="n">
+        <v>4496.6</v>
+      </c>
+      <c r="C16" t="n">
+        <v>4383</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="E16" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="F16" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.69</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B17" t="n">
+        <v>4428.5</v>
+      </c>
+      <c r="C17" t="n">
+        <v>4408.9</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F17" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B18" t="n">
+        <v>4446.7</v>
+      </c>
+      <c r="C18" t="n">
+        <v>4363.6</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="F18" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B19" t="n">
+        <v>4460.5</v>
+      </c>
+      <c r="C19" t="n">
+        <v>4380.4</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="F19" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.03</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B20" t="n">
+        <v>4445.3</v>
+      </c>
+      <c r="C20" t="n">
+        <v>4417.8</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="F20" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B21" t="n">
+        <v>4423.4</v>
+      </c>
+      <c r="C21" t="n">
+        <v>4366</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F21" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B22" t="n">
+        <v>4536.8</v>
+      </c>
+      <c r="C22" t="n">
+        <v>4489.4</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="F22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.97</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B23" t="n">
+        <v>4660.3</v>
+      </c>
+      <c r="C23" t="n">
+        <v>4516.3</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="E23" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="F23" t="n">
+        <v>15.17</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2.03</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B24" t="n">
+        <v>4723.3</v>
+      </c>
+      <c r="C24" t="n">
+        <v>4624.1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="E24" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="F24" t="n">
+        <v>16.12</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B25" t="n">
+        <v>4700</v>
+      </c>
+      <c r="C25" t="n">
+        <v>4640.8</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="E25" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="F25" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2.21</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B26" t="n">
+        <v>4673.3</v>
+      </c>
+      <c r="C26" t="n">
+        <v>4638.1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>15.78</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B27" t="n">
+        <v>4657.3</v>
+      </c>
+      <c r="C27" t="n">
+        <v>4598.2</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="F27" t="n">
+        <v>15.43</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B28" t="n">
+        <v>4504.1</v>
+      </c>
+      <c r="C28" t="n">
+        <v>4609.7</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-2.29</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="F28" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B29" t="n">
+        <v>4480.5</v>
+      </c>
+      <c r="C29" t="n">
+        <v>4478.1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-3.45</v>
+      </c>
+      <c r="F29" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B30" t="n">
+        <v>4407.7</v>
+      </c>
+      <c r="C30" t="n">
+        <v>4431.1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-4.97</v>
+      </c>
+      <c r="F30" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.33</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B31" t="n">
+        <v>4434.3</v>
+      </c>
+      <c r="C31" t="n">
+        <v>4348</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-3.56</v>
+      </c>
+      <c r="F31" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B32" t="n">
+        <v>4525.4</v>
+      </c>
+      <c r="C32" t="n">
+        <v>4366.3</v>
+      </c>
+      <c r="D32" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-1.83</v>
+      </c>
+      <c r="F32" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2.41</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B33" t="n">
+        <v>4478.4</v>
+      </c>
+      <c r="C33" t="n">
+        <v>4491.7</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F33" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B34" t="n">
+        <v>4476.6</v>
+      </c>
+      <c r="C34" t="n">
+        <v>4429.8</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="F34" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B35" t="n">
+        <v>4441.3</v>
+      </c>
+      <c r="C35" t="n">
+        <v>4429.8</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B36" t="n">
+        <v>4466.2</v>
+      </c>
+      <c r="C36" t="n">
+        <v>4393.9</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B37" t="n">
+        <v>4405</v>
+      </c>
+      <c r="C37" t="n">
+        <v>4416</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B38" t="n">
+        <v>4426.3</v>
+      </c>
+      <c r="C38" t="n">
+        <v>4364.5</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B39" t="n">
+        <v>4337.1</v>
+      </c>
+      <c r="C39" t="n">
+        <v>4366.2</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B40" t="n">
+        <v>4316.9</v>
+      </c>
+      <c r="C40" t="n">
+        <v>4351.9</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="F40" t="n">
+        <v>-2.71</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B41" t="n">
+        <v>4391.7</v>
+      </c>
+      <c r="C41" t="n">
+        <v>4332.8</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="F41" t="n">
+        <v>-1.83</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B42" t="n">
+        <v>4392.9</v>
+      </c>
+      <c r="C42" t="n">
+        <v>4387.5</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="F42" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-3.79</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B43" t="n">
+        <v>4392.2</v>
+      </c>
+      <c r="C43" t="n">
+        <v>4399.7</v>
+      </c>
+      <c r="D43" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="F43" t="n">
+        <v>-3.37</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B44" t="n">
+        <v>4393</v>
+      </c>
+      <c r="C44" t="n">
+        <v>4424.9</v>
+      </c>
+      <c r="D44" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F44" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B45" t="n">
+        <v>4362.8</v>
+      </c>
+      <c r="C45" t="n">
+        <v>4383.9</v>
+      </c>
+      <c r="D45" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="F45" t="n">
+        <v>-6.79</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B46" t="n">
+        <v>4327.6</v>
+      </c>
+      <c r="C46" t="n">
+        <v>4376.4</v>
+      </c>
+      <c r="D46" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-1.37</v>
+      </c>
+      <c r="F46" t="n">
+        <v>-7.88</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B47" t="n">
+        <v>4280.8</v>
+      </c>
+      <c r="C47" t="n">
+        <v>4318.4</v>
+      </c>
+      <c r="D47" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="F47" t="n">
+        <v>-8.81</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B48" t="n">
+        <v>4314.3</v>
+      </c>
+      <c r="C48" t="n">
+        <v>4298</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E48" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="F48" t="n">
+        <v>-7.29</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B49" t="n">
+        <v>4167.6</v>
+      </c>
+      <c r="C49" t="n">
+        <v>4321.2</v>
+      </c>
+      <c r="D49" t="n">
+        <v>-3.55</v>
+      </c>
+      <c r="E49" t="n">
+        <v>-4.93</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-10.64</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B50" t="n">
+        <v>4184.4</v>
+      </c>
+      <c r="C50" t="n">
+        <v>4321.2</v>
+      </c>
+      <c r="D50" t="n">
+        <v>-3.17</v>
+      </c>
+      <c r="E50" t="n">
+        <v>-4.55</v>
+      </c>
+      <c r="F50" t="n">
+        <v>-10.28</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-6.69</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B51" t="n">
+        <v>4188.4</v>
+      </c>
+      <c r="C51" t="n">
+        <v>4179.7</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-3.01</v>
+      </c>
+      <c r="F51" t="n">
+        <v>-6.54</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B52" t="n">
+        <v>4191.4</v>
+      </c>
+      <c r="C52" t="n">
+        <v>4186.7</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E52" t="n">
+        <v>-2.48</v>
+      </c>
+      <c r="F52" t="n">
+        <v>-4.66</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B53" t="n">
+        <v>4164.2</v>
+      </c>
+      <c r="C53" t="n">
+        <v>4202.3</v>
+      </c>
+      <c r="D53" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="E53" t="n">
+        <v>-3.63</v>
+      </c>
+      <c r="F53" t="n">
+        <v>-5.67</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B54" t="n">
+        <v>4167.9</v>
+      </c>
+      <c r="C54" t="n">
+        <v>4162.3</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E54" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F54" t="n">
+        <v>-8.19</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B55" t="n">
+        <v>4186.7</v>
+      </c>
+      <c r="C55" t="n">
+        <v>4156.8</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F55" t="n">
+        <v>-6.48</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B56" t="n">
+        <v>4146.9</v>
+      </c>
+      <c r="C56" t="n">
+        <v>4187.1</v>
+      </c>
+      <c r="D56" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="E56" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="F56" t="n">
+        <v>-6.58</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B57" t="n">
+        <v>4170.1</v>
+      </c>
+      <c r="C57" t="n">
+        <v>4140.7</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="E57" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="F57" t="n">
+        <v>-6.51</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B58" t="n">
+        <v>4216.3</v>
+      </c>
+      <c r="C58" t="n">
+        <v>4157</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-4.33</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B59" t="n">
+        <v>4191.4</v>
+      </c>
+      <c r="C59" t="n">
+        <v>4216.3</v>
+      </c>
+      <c r="D59" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="F59" t="n">
+        <v>-4.93</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B60" t="n">
+        <v>4177.1</v>
+      </c>
+      <c r="C60" t="n">
+        <v>4190.6</v>
+      </c>
+      <c r="D60" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="E60" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="F60" t="n">
+        <v>-4.02</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B61" t="n">
+        <v>4108.7</v>
+      </c>
+      <c r="C61" t="n">
+        <v>4177.3</v>
+      </c>
+      <c r="D61" t="n">
+        <v>-1.64</v>
+      </c>
+      <c r="E61" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="F61" t="n">
+        <v>-5.17</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B62" t="n">
+        <v>4176.7</v>
+      </c>
+      <c r="C62" t="n">
+        <v>4107.9</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F62" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B63" t="n">
+        <v>4207</v>
+      </c>
+      <c r="C63" t="n">
+        <v>4170.1</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E63" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="F63" t="n">
+        <v>-4.38</v>
+      </c>
+      <c r="G63" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B64" t="n">
+        <v>4159.7</v>
+      </c>
+      <c r="C64" t="n">
+        <v>4181.1</v>
+      </c>
+      <c r="D64" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="E64" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="F64" t="n">
+        <v>-5.99</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B65" t="n">
+        <v>4161</v>
+      </c>
+      <c r="C65" t="n">
+        <v>4160.1</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E65" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="F65" t="n">
+        <v>-5.08</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4380,22 +5923,22 @@
         <v>46227</v>
       </c>
       <c r="B2" t="n">
-        <v>4046.6</v>
+        <v>51711.65</v>
       </c>
       <c r="C2" t="n">
-        <v>4070.8</v>
+        <v>51947.25</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6</v>
+        <v>0.46</v>
       </c>
       <c r="E2" t="n">
-        <v>1.45</v>
+        <v>-0.38</v>
       </c>
       <c r="F2" t="n">
-        <v>2.02</v>
+        <v>0.19</v>
       </c>
       <c r="G2" t="n">
-        <v>0.29</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="3">
@@ -4403,22 +5946,22 @@
         <v>46227</v>
       </c>
       <c r="B3" t="n">
-        <v>4046.6</v>
+        <v>51711.65</v>
       </c>
       <c r="C3" t="n">
-        <v>4070.8</v>
+        <v>51947.25</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6</v>
+        <v>0.46</v>
       </c>
       <c r="E3" t="n">
-        <v>1.45</v>
+        <v>-0.38</v>
       </c>
       <c r="F3" t="n">
-        <v>2.02</v>
+        <v>0.19</v>
       </c>
       <c r="G3" t="n">
-        <v>0.29</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="4">
@@ -4426,22 +5969,22 @@
         <v>46230</v>
       </c>
       <c r="B4" t="n">
-        <v>4074.5</v>
+        <v>52210.08</v>
       </c>
       <c r="C4" t="n">
-        <v>4067.6</v>
+        <v>51947.25</v>
       </c>
       <c r="D4" t="n">
-        <v>0.17</v>
+        <v>0.51</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6</v>
+        <v>0.72</v>
       </c>
       <c r="F4" t="n">
-        <v>1.09</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>0.93</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="5">
@@ -4449,22 +5992,22 @@
         <v>46231</v>
       </c>
       <c r="B5" t="n">
-        <v>4028.8</v>
+        <v>52747.32</v>
       </c>
       <c r="C5" t="n">
-        <v>4074.5</v>
+        <v>52210.08</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.12</v>
+        <v>1.03</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.04</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.22</v>
+        <v>1.68</v>
       </c>
       <c r="G5" t="n">
-        <v>0.39</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="6">
@@ -4472,22 +6015,22 @@
         <v>46232</v>
       </c>
       <c r="B6" t="n">
-        <v>4069.1</v>
+        <v>51818.64</v>
       </c>
       <c r="C6" t="n">
-        <v>4036.3</v>
+        <v>52747.32</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8100000000000001</v>
+        <v>-1.76</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.88</v>
+        <v>-0.77</v>
       </c>
       <c r="F6" t="n">
-        <v>1.16</v>
+        <v>-0.7</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.65</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="7">
@@ -4495,22 +6038,22 @@
         <v>46233</v>
       </c>
       <c r="B7" t="n">
-        <v>4173.6</v>
+        <v>52006.44</v>
       </c>
       <c r="C7" t="n">
-        <v>4034.7</v>
+        <v>51594.14</v>
       </c>
       <c r="D7" t="n">
-        <v>3.44</v>
+        <v>0.8</v>
       </c>
       <c r="E7" t="n">
-        <v>3.14</v>
+        <v>0.57</v>
       </c>
       <c r="F7" t="n">
-        <v>3.75</v>
+        <v>-0.6</v>
       </c>
       <c r="G7" t="n">
-        <v>3.87</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="8">
@@ -4518,22 +6061,22 @@
         <v>46234</v>
       </c>
       <c r="B8" t="n">
-        <v>4101.2</v>
+        <v>52407.88</v>
       </c>
       <c r="C8" t="n">
-        <v>4100.1</v>
+        <v>52208.06</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03</v>
+        <v>0.38</v>
       </c>
       <c r="E8" t="n">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="G8" t="n">
-        <v>2.54</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="9">
@@ -4541,22 +6084,22 @@
         <v>46237</v>
       </c>
       <c r="B9" t="n">
-        <v>4090.3</v>
+        <v>52996.27</v>
       </c>
       <c r="C9" t="n">
-        <v>4049.1</v>
+        <v>52485.03</v>
       </c>
       <c r="D9" t="n">
-        <v>1.02</v>
+        <v>0.97</v>
       </c>
       <c r="E9" t="n">
-        <v>0.39</v>
+        <v>1.51</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.54</v>
+        <v>0.18</v>
       </c>
       <c r="G9" t="n">
-        <v>3.46</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="10">
@@ -4564,22 +6107,22 @@
         <v>46238</v>
       </c>
       <c r="B10" t="n">
-        <v>4150.4</v>
+        <v>54173.91</v>
       </c>
       <c r="C10" t="n">
-        <v>4033.7</v>
+        <v>53178.41</v>
       </c>
       <c r="D10" t="n">
-        <v>2.89</v>
+        <v>1.87</v>
       </c>
       <c r="E10" t="n">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.11</v>
+        <v>2.11</v>
       </c>
       <c r="G10" t="n">
-        <v>3.53</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="11">
@@ -4587,22 +6130,22 @@
         <v>46239</v>
       </c>
       <c r="B11" t="n">
-        <v>4293</v>
+        <v>54544.79</v>
       </c>
       <c r="C11" t="n">
-        <v>4095.4</v>
+        <v>54085.88</v>
       </c>
       <c r="D11" t="n">
-        <v>4.82</v>
+        <v>0.85</v>
       </c>
       <c r="E11" t="n">
-        <v>6.4</v>
+        <v>5.72</v>
       </c>
       <c r="F11" t="n">
-        <v>3.56</v>
+        <v>3.06</v>
       </c>
       <c r="G11" t="n">
-        <v>1.78</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -4610,22 +6153,22 @@
         <v>46240</v>
       </c>
       <c r="B12" t="n">
-        <v>4242</v>
+        <v>53885.1</v>
       </c>
       <c r="C12" t="n">
-        <v>4245.8</v>
+        <v>54349.12</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.09</v>
+        <v>-0.85</v>
       </c>
       <c r="E12" t="n">
-        <v>3.46</v>
+        <v>3.21</v>
       </c>
       <c r="F12" t="n">
-        <v>4.2</v>
+        <v>2.94</v>
       </c>
       <c r="G12" t="n">
-        <v>2.23</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="13">
@@ -4633,22 +6176,22 @@
         <v>46241</v>
       </c>
       <c r="B13" t="n">
-        <v>4397</v>
+        <v>53987.31</v>
       </c>
       <c r="C13" t="n">
-        <v>4242</v>
+        <v>53885.1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.65</v>
+        <v>0.19</v>
       </c>
       <c r="E13" t="n">
-        <v>8.59</v>
+        <v>2.86</v>
       </c>
       <c r="F13" t="n">
-        <v>6.45</v>
+        <v>2.86</v>
       </c>
       <c r="G13" t="n">
-        <v>2.2</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="14">
@@ -4656,22 +6199,22 @@
         <v>46244</v>
       </c>
       <c r="B14" t="n">
-        <v>4401.4</v>
+        <v>53969.28</v>
       </c>
       <c r="C14" t="n">
-        <v>4340.7</v>
+        <v>54036.93</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4</v>
+        <v>-0.13</v>
       </c>
       <c r="E14" t="n">
-        <v>9.119999999999999</v>
+        <v>1.49</v>
       </c>
       <c r="F14" t="n">
-        <v>7.24</v>
+        <v>2.53</v>
       </c>
       <c r="G14" t="n">
-        <v>2.2</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="15">
@@ -4679,22 +6222,22 @@
         <v>46245</v>
       </c>
       <c r="B15" t="n">
-        <v>4442.2</v>
+        <v>54016.06</v>
       </c>
       <c r="C15" t="n">
-        <v>4361.8</v>
+        <v>53975.98</v>
       </c>
       <c r="D15" t="n">
-        <v>1.84</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>8.470000000000001</v>
+        <v>-0.13</v>
       </c>
       <c r="F15" t="n">
-        <v>11.14</v>
+        <v>2.89</v>
       </c>
       <c r="G15" t="n">
-        <v>3.22</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="16">
@@ -4702,22 +6245,22 @@
         <v>46246</v>
       </c>
       <c r="B16" t="n">
-        <v>4496.6</v>
+        <v>53795.51</v>
       </c>
       <c r="C16" t="n">
-        <v>4383</v>
+        <v>53791.85</v>
       </c>
       <c r="D16" t="n">
-        <v>2.59</v>
+        <v>0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>5.91</v>
+        <v>-1.02</v>
       </c>
       <c r="F16" t="n">
-        <v>10.72</v>
+        <v>2.45</v>
       </c>
       <c r="G16" t="n">
-        <v>1.69</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="17">
@@ -4725,22 +6268,22 @@
         <v>46247</v>
       </c>
       <c r="B17" t="n">
-        <v>4428.5</v>
+        <v>53964.83</v>
       </c>
       <c r="C17" t="n">
-        <v>4408.9</v>
+        <v>53770.27</v>
       </c>
       <c r="D17" t="n">
-        <v>0.44</v>
+        <v>0.36</v>
       </c>
       <c r="E17" t="n">
-        <v>4.4</v>
+        <v>0.15</v>
       </c>
       <c r="F17" t="n">
-        <v>9.51</v>
+        <v>2.52</v>
       </c>
       <c r="G17" t="n">
-        <v>2.16</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="18">
@@ -4748,45 +6291,30 @@
         <v>46248</v>
       </c>
       <c r="B18" t="n">
-        <v>4446.7</v>
+        <v>53804.83</v>
       </c>
       <c r="C18" t="n">
-        <v>4363.6</v>
+        <v>53839.99</v>
       </c>
       <c r="D18" t="n">
-        <v>1.9</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>2.44</v>
+        <v>-0.43</v>
       </c>
       <c r="F18" t="n">
-        <v>11.57</v>
+        <v>2.49</v>
       </c>
       <c r="G18" t="n">
-        <v>1.65</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
         <v>46251</v>
       </c>
-      <c r="B19" t="n">
-        <v>4460.5</v>
-      </c>
       <c r="C19" t="n">
-        <v>4380.4</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="E19" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="F19" t="n">
-        <v>11.16</v>
-      </c>
-      <c r="G19" t="n">
-        <v>2.03</v>
+        <v>53732.41</v>
       </c>
     </row>
     <row r="20">
@@ -4794,22 +6322,22 @@
         <v>46252</v>
       </c>
       <c r="B20" t="n">
-        <v>4445.3</v>
+        <v>53343.4</v>
       </c>
       <c r="C20" t="n">
-        <v>4417.8</v>
+        <v>53459.78</v>
       </c>
       <c r="D20" t="n">
-        <v>0.62</v>
+        <v>-0.22</v>
       </c>
       <c r="E20" t="n">
-        <v>1.42</v>
+        <v>-0.83</v>
       </c>
       <c r="F20" t="n">
-        <v>10.85</v>
+        <v>2.9</v>
       </c>
       <c r="G20" t="n">
-        <v>1.91</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="21">
@@ -4817,22 +6345,22 @@
         <v>46253</v>
       </c>
       <c r="B21" t="n">
-        <v>4423.4</v>
+        <v>53463.05</v>
       </c>
       <c r="C21" t="n">
-        <v>4366</v>
+        <v>53343.4</v>
       </c>
       <c r="D21" t="n">
-        <v>1.31</v>
+        <v>0.22</v>
       </c>
       <c r="E21" t="n">
-        <v>0.33</v>
+        <v>-0.57</v>
       </c>
       <c r="F21" t="n">
-        <v>8.65</v>
+        <v>2.37</v>
       </c>
       <c r="G21" t="n">
-        <v>0.89</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="22">
@@ -4840,22 +6368,22 @@
         <v>46254</v>
       </c>
       <c r="B22" t="n">
-        <v>4536.8</v>
+        <v>52759.21</v>
       </c>
       <c r="C22" t="n">
-        <v>4489.4</v>
+        <v>53463.05</v>
       </c>
       <c r="D22" t="n">
-        <v>1.06</v>
+        <v>-1.32</v>
       </c>
       <c r="E22" t="n">
-        <v>3.97</v>
+        <v>-2.01</v>
       </c>
       <c r="F22" t="n">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="G22" t="n">
-        <v>2.97</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="23">
@@ -4863,22 +6391,22 @@
         <v>46255</v>
       </c>
       <c r="B23" t="n">
-        <v>4660.3</v>
+        <v>53277.01</v>
       </c>
       <c r="C23" t="n">
-        <v>4516.3</v>
+        <v>52759.21</v>
       </c>
       <c r="D23" t="n">
-        <v>3.19</v>
+        <v>0.98</v>
       </c>
       <c r="E23" t="n">
-        <v>6.39</v>
+        <v>-0.85</v>
       </c>
       <c r="F23" t="n">
-        <v>15.17</v>
+        <v>3.03</v>
       </c>
       <c r="G23" t="n">
-        <v>2.03</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="24">
@@ -4886,22 +6414,22 @@
         <v>46258</v>
       </c>
       <c r="B24" t="n">
-        <v>4723.3</v>
+        <v>53417.16</v>
       </c>
       <c r="C24" t="n">
-        <v>4624.1</v>
+        <v>53277.01</v>
       </c>
       <c r="D24" t="n">
-        <v>2.15</v>
+        <v>0.26</v>
       </c>
       <c r="E24" t="n">
-        <v>6.92</v>
+        <v>-0.08</v>
       </c>
       <c r="F24" t="n">
-        <v>16.12</v>
+        <v>2.83</v>
       </c>
       <c r="G24" t="n">
-        <v>1.57</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="25">
@@ -4909,22 +6437,22 @@
         <v>46259</v>
       </c>
       <c r="B25" t="n">
-        <v>4700</v>
+        <v>53577.4</v>
       </c>
       <c r="C25" t="n">
-        <v>4640.8</v>
+        <v>53417.16</v>
       </c>
       <c r="D25" t="n">
-        <v>1.28</v>
+        <v>0.3</v>
       </c>
       <c r="E25" t="n">
-        <v>7.65</v>
+        <v>0.44</v>
       </c>
       <c r="F25" t="n">
-        <v>15.35</v>
+        <v>2.62</v>
       </c>
       <c r="G25" t="n">
-        <v>2.21</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="26">
@@ -4932,22 +6460,22 @@
         <v>46260</v>
       </c>
       <c r="B26" t="n">
-        <v>4673.3</v>
+        <v>53463.88</v>
       </c>
       <c r="C26" t="n">
-        <v>4638.1</v>
+        <v>53577.4</v>
       </c>
       <c r="D26" t="n">
-        <v>0.76</v>
+        <v>-0.21</v>
       </c>
       <c r="E26" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>15.78</v>
+        <v>1.36</v>
       </c>
       <c r="G26" t="n">
-        <v>2.8</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="27">
@@ -4955,22 +6483,22 @@
         <v>46261</v>
       </c>
       <c r="B27" t="n">
-        <v>4657.3</v>
+        <v>53569.44</v>
       </c>
       <c r="C27" t="n">
-        <v>4598.2</v>
+        <v>53463.88</v>
       </c>
       <c r="D27" t="n">
-        <v>1.29</v>
+        <v>0.2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.12</v>
+        <v>1.54</v>
       </c>
       <c r="F27" t="n">
-        <v>15.43</v>
+        <v>3.83</v>
       </c>
       <c r="G27" t="n">
-        <v>1.88</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="28">
@@ -4978,22 +6506,22 @@
         <v>46262</v>
       </c>
       <c r="B28" t="n">
-        <v>4504.1</v>
+        <v>53559.99</v>
       </c>
       <c r="C28" t="n">
-        <v>4609.7</v>
+        <v>53569.44</v>
       </c>
       <c r="D28" t="n">
-        <v>-2.29</v>
+        <v>-0.02</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.6</v>
+        <v>0.53</v>
       </c>
       <c r="F28" t="n">
-        <v>9.85</v>
+        <v>2.59</v>
       </c>
       <c r="G28" t="n">
-        <v>1.7</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="29">
@@ -5001,22 +6529,22 @@
         <v>46265</v>
       </c>
       <c r="B29" t="n">
-        <v>4480.5</v>
+        <v>53212.7</v>
       </c>
       <c r="C29" t="n">
-        <v>4478.1</v>
+        <v>53559.99</v>
       </c>
       <c r="D29" t="n">
-        <v>0.05</v>
+        <v>-0.65</v>
       </c>
       <c r="E29" t="n">
-        <v>-3.45</v>
+        <v>-0.38</v>
       </c>
       <c r="F29" t="n">
-        <v>10.65</v>
+        <v>1.39</v>
       </c>
       <c r="G29" t="n">
-        <v>0.19</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="30">
@@ -5024,22 +6552,22 @@
         <v>46266</v>
       </c>
       <c r="B30" t="n">
-        <v>4407.7</v>
+        <v>52960.85</v>
       </c>
       <c r="C30" t="n">
-        <v>4431.1</v>
+        <v>53185.9</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.53</v>
+        <v>-0.42</v>
       </c>
       <c r="E30" t="n">
-        <v>-4.97</v>
+        <v>-0.85</v>
       </c>
       <c r="F30" t="n">
-        <v>9.27</v>
+        <v>0.91</v>
       </c>
       <c r="G30" t="n">
-        <v>2.33</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="31">
@@ -5047,22 +6575,22 @@
         <v>46267</v>
       </c>
       <c r="B31" t="n">
-        <v>4434.3</v>
+        <v>53171.82</v>
       </c>
       <c r="C31" t="n">
-        <v>4348</v>
+        <v>52766.88</v>
       </c>
       <c r="D31" t="n">
-        <v>1.98</v>
+        <v>0.77</v>
       </c>
       <c r="E31" t="n">
-        <v>-3.56</v>
+        <v>-0.55</v>
       </c>
       <c r="F31" t="n">
-        <v>8.279999999999999</v>
+        <v>-1.69</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="32">
@@ -5070,22 +6598,22 @@
         <v>46268</v>
       </c>
       <c r="B32" t="n">
-        <v>4525.4</v>
+        <v>53412.4</v>
       </c>
       <c r="C32" t="n">
-        <v>4366.3</v>
+        <v>53061.95</v>
       </c>
       <c r="D32" t="n">
-        <v>3.64</v>
+        <v>0.66</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.83</v>
+        <v>-0.1</v>
       </c>
       <c r="F32" t="n">
-        <v>6.59</v>
+        <v>-1.25</v>
       </c>
       <c r="G32" t="n">
-        <v>2.41</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="33">
@@ -5093,1491 +6621,6 @@
         <v>46269</v>
       </c>
       <c r="B33" t="n">
-        <v>4478.4</v>
-      </c>
-      <c r="C33" t="n">
-        <v>4491.7</v>
-      </c>
-      <c r="D33" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="F33" t="n">
-        <v>5.57</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>46272</v>
-      </c>
-      <c r="B34" t="n">
-        <v>4476.6</v>
-      </c>
-      <c r="C34" t="n">
-        <v>4429.8</v>
-      </c>
-      <c r="D34" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="E34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="F34" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="G34" t="n">
-        <v>1.14</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>46273</v>
-      </c>
-      <c r="B35" t="n">
-        <v>4441.3</v>
-      </c>
-      <c r="C35" t="n">
-        <v>4429.8</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="F35" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="G35" t="n">
-        <v>1.14</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>46274</v>
-      </c>
-      <c r="B36" t="n">
-        <v>4466.2</v>
-      </c>
-      <c r="C36" t="n">
-        <v>4393.9</v>
-      </c>
-      <c r="D36" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="E36" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="F36" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>46275</v>
-      </c>
-      <c r="B37" t="n">
-        <v>4405</v>
-      </c>
-      <c r="C37" t="n">
-        <v>4416</v>
-      </c>
-      <c r="D37" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G37" t="n">
-        <v>1.04</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>46276</v>
-      </c>
-      <c r="B38" t="n">
-        <v>4426.3</v>
-      </c>
-      <c r="C38" t="n">
-        <v>4364.5</v>
-      </c>
-      <c r="D38" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="E38" t="n">
-        <v>-1.46</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="G38" t="n">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="B39" t="n">
-        <v>4337.1</v>
-      </c>
-      <c r="C39" t="n">
-        <v>4366.2</v>
-      </c>
-      <c r="D39" t="n">
-        <v>-0.67</v>
-      </c>
-      <c r="E39" t="n">
-        <v>-2.09</v>
-      </c>
-      <c r="F39" t="n">
-        <v>-0.61</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="B40" t="n">
-        <v>4316.9</v>
-      </c>
-      <c r="C40" t="n">
-        <v>4351.9</v>
-      </c>
-      <c r="D40" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="E40" t="n">
-        <v>-2.75</v>
-      </c>
-      <c r="F40" t="n">
-        <v>-2.71</v>
-      </c>
-      <c r="G40" t="n">
-        <v>-0.51</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="B41" t="n">
-        <v>4391.7</v>
-      </c>
-      <c r="C41" t="n">
-        <v>4332.8</v>
-      </c>
-      <c r="D41" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="E41" t="n">
-        <v>-1.55</v>
-      </c>
-      <c r="F41" t="n">
-        <v>-1.83</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="B42" t="n">
-        <v>4392.9</v>
-      </c>
-      <c r="C42" t="n">
-        <v>4387.5</v>
-      </c>
-      <c r="D42" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E42" t="n">
-        <v>-0.33</v>
-      </c>
-      <c r="F42" t="n">
-        <v>-0.63</v>
-      </c>
-      <c r="G42" t="n">
-        <v>-3.79</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="B43" t="n">
-        <v>4392.2</v>
-      </c>
-      <c r="C43" t="n">
-        <v>4399.7</v>
-      </c>
-      <c r="D43" t="n">
-        <v>-0.17</v>
-      </c>
-      <c r="E43" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="F43" t="n">
-        <v>-3.37</v>
-      </c>
-      <c r="G43" t="n">
-        <v>-0.63</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B44" t="n">
-        <v>4393</v>
-      </c>
-      <c r="C44" t="n">
-        <v>4424.9</v>
-      </c>
-      <c r="D44" t="n">
-        <v>-0.72</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="F44" t="n">
-        <v>-3.9</v>
-      </c>
-      <c r="G44" t="n">
-        <v>-0.44</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="n">
-        <v>46287</v>
-      </c>
-      <c r="B45" t="n">
-        <v>4362.8</v>
-      </c>
-      <c r="C45" t="n">
-        <v>4383.9</v>
-      </c>
-      <c r="D45" t="n">
-        <v>-0.48</v>
-      </c>
-      <c r="E45" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="F45" t="n">
-        <v>-6.79</v>
-      </c>
-      <c r="G45" t="n">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="B46" t="n">
-        <v>4327.6</v>
-      </c>
-      <c r="C46" t="n">
-        <v>4376.4</v>
-      </c>
-      <c r="D46" t="n">
-        <v>-1.12</v>
-      </c>
-      <c r="E46" t="n">
-        <v>-1.37</v>
-      </c>
-      <c r="F46" t="n">
-        <v>-7.88</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="B47" t="n">
-        <v>4280.8</v>
-      </c>
-      <c r="C47" t="n">
-        <v>4318.4</v>
-      </c>
-      <c r="D47" t="n">
-        <v>-0.87</v>
-      </c>
-      <c r="E47" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="F47" t="n">
-        <v>-8.81</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="B48" t="n">
-        <v>4314.3</v>
-      </c>
-      <c r="C48" t="n">
-        <v>4298</v>
-      </c>
-      <c r="D48" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E48" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="F48" t="n">
-        <v>-7.29</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B49" t="n">
-        <v>4167.6</v>
-      </c>
-      <c r="C49" t="n">
-        <v>4321.2</v>
-      </c>
-      <c r="D49" t="n">
-        <v>-3.55</v>
-      </c>
-      <c r="E49" t="n">
-        <v>-4.93</v>
-      </c>
-      <c r="F49" t="n">
-        <v>-10.64</v>
-      </c>
-      <c r="G49" t="n">
-        <v>-0.24</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="B50" t="n">
-        <v>4184.4</v>
-      </c>
-      <c r="C50" t="n">
-        <v>4321.2</v>
-      </c>
-      <c r="D50" t="n">
-        <v>-3.17</v>
-      </c>
-      <c r="E50" t="n">
-        <v>-4.55</v>
-      </c>
-      <c r="F50" t="n">
-        <v>-10.28</v>
-      </c>
-      <c r="G50" t="n">
-        <v>-6.69</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B51" t="n">
-        <v>4188.4</v>
-      </c>
-      <c r="C51" t="n">
-        <v>4179.7</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E51" t="n">
-        <v>-3.01</v>
-      </c>
-      <c r="F51" t="n">
-        <v>-6.54</v>
-      </c>
-      <c r="G51" t="n">
-        <v>1.49</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="B52" t="n">
-        <v>4191.4</v>
-      </c>
-      <c r="C52" t="n">
-        <v>4186.7</v>
-      </c>
-      <c r="D52" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E52" t="n">
-        <v>-2.48</v>
-      </c>
-      <c r="F52" t="n">
-        <v>-4.66</v>
-      </c>
-      <c r="G52" t="n">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="B53" t="n">
-        <v>4164.2</v>
-      </c>
-      <c r="C53" t="n">
-        <v>4202.3</v>
-      </c>
-      <c r="D53" t="n">
-        <v>-0.91</v>
-      </c>
-      <c r="E53" t="n">
-        <v>-3.63</v>
-      </c>
-      <c r="F53" t="n">
-        <v>-5.67</v>
-      </c>
-      <c r="G53" t="n">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="B54" t="n">
-        <v>4167.9</v>
-      </c>
-      <c r="C54" t="n">
-        <v>4162.3</v>
-      </c>
-      <c r="D54" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="E54" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="F54" t="n">
-        <v>-8.19</v>
-      </c>
-      <c r="G54" t="n">
-        <v>0.28</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="B55" t="n">
-        <v>4186.7</v>
-      </c>
-      <c r="C55" t="n">
-        <v>4156.8</v>
-      </c>
-      <c r="D55" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E55" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="F55" t="n">
-        <v>-6.48</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0.49</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="B56" t="n">
-        <v>4146.9</v>
-      </c>
-      <c r="C56" t="n">
-        <v>4187.1</v>
-      </c>
-      <c r="D56" t="n">
-        <v>-0.96</v>
-      </c>
-      <c r="E56" t="n">
-        <v>-0.95</v>
-      </c>
-      <c r="F56" t="n">
-        <v>-6.58</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="B57" t="n">
-        <v>4170.1</v>
-      </c>
-      <c r="C57" t="n">
-        <v>4140.7</v>
-      </c>
-      <c r="D57" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="E57" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="F57" t="n">
-        <v>-6.51</v>
-      </c>
-      <c r="G57" t="n">
-        <v>-0.03</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="B58" t="n">
-        <v>4216.3</v>
-      </c>
-      <c r="C58" t="n">
-        <v>4157</v>
-      </c>
-      <c r="D58" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="E58" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-4.33</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="B59" t="n">
-        <v>4191.4</v>
-      </c>
-      <c r="C59" t="n">
-        <v>4216.3</v>
-      </c>
-      <c r="D59" t="n">
-        <v>-0.59</v>
-      </c>
-      <c r="E59" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="F59" t="n">
-        <v>-4.93</v>
-      </c>
-      <c r="G59" t="n">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B60" t="n">
-        <v>4177.1</v>
-      </c>
-      <c r="C60" t="n">
-        <v>4190.6</v>
-      </c>
-      <c r="D60" t="n">
-        <v>-0.32</v>
-      </c>
-      <c r="E60" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="F60" t="n">
-        <v>-4.02</v>
-      </c>
-      <c r="G60" t="n">
-        <v>0.21</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="1" t="n">
-        <v>46309</v>
-      </c>
-      <c r="B61" t="n">
-        <v>4108.7</v>
-      </c>
-      <c r="C61" t="n">
-        <v>4177.3</v>
-      </c>
-      <c r="D61" t="n">
-        <v>-1.64</v>
-      </c>
-      <c r="E61" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="F61" t="n">
-        <v>-5.17</v>
-      </c>
-      <c r="G61" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="1" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B62" t="n">
-        <v>4176.7</v>
-      </c>
-      <c r="C62" t="n">
-        <v>4107.9</v>
-      </c>
-      <c r="D62" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="E62" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="F62" t="n">
-        <v>-4.8</v>
-      </c>
-      <c r="G62" t="n">
-        <v>0.91</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="1" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B63" t="n">
-        <v>4207</v>
-      </c>
-      <c r="C63" t="n">
-        <v>4170.1</v>
-      </c>
-      <c r="D63" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="E63" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="F63" t="n">
-        <v>-4.38</v>
-      </c>
-      <c r="G63" t="n">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="B64" t="n">
-        <v>4159.7</v>
-      </c>
-      <c r="C64" t="n">
-        <v>4181.1</v>
-      </c>
-      <c r="D64" t="n">
-        <v>-0.51</v>
-      </c>
-      <c r="E64" t="n">
-        <v>-0.74</v>
-      </c>
-      <c r="F64" t="n">
-        <v>-5.99</v>
-      </c>
-      <c r="G64" t="n">
-        <v>0.32</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G63"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Prev Price</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Today Price</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Change %</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Weekly Ret %</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Monthly Ret %</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Z Score</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>46227</v>
-      </c>
-      <c r="B2" t="n">
-        <v>51711.65</v>
-      </c>
-      <c r="C2" t="n">
-        <v>51947.25</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>46227</v>
-      </c>
-      <c r="B3" t="n">
-        <v>51711.65</v>
-      </c>
-      <c r="C3" t="n">
-        <v>51947.25</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>46230</v>
-      </c>
-      <c r="B4" t="n">
-        <v>52210.08</v>
-      </c>
-      <c r="C4" t="n">
-        <v>51947.25</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>46231</v>
-      </c>
-      <c r="B5" t="n">
-        <v>52747.32</v>
-      </c>
-      <c r="C5" t="n">
-        <v>52210.08</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>46232</v>
-      </c>
-      <c r="B6" t="n">
-        <v>51818.64</v>
-      </c>
-      <c r="C6" t="n">
-        <v>52747.32</v>
-      </c>
-      <c r="D6" t="n">
-        <v>-1.76</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="F6" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-0.37</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>46233</v>
-      </c>
-      <c r="B7" t="n">
-        <v>52006.44</v>
-      </c>
-      <c r="C7" t="n">
-        <v>51594.14</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2.64</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="B8" t="n">
-        <v>52407.88</v>
-      </c>
-      <c r="C8" t="n">
-        <v>52208.06</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>46237</v>
-      </c>
-      <c r="B9" t="n">
-        <v>52996.27</v>
-      </c>
-      <c r="C9" t="n">
-        <v>52485.03</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.19</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="B10" t="n">
-        <v>54173.91</v>
-      </c>
-      <c r="C10" t="n">
-        <v>53178.41</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="E10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="F10" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1.93</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>46239</v>
-      </c>
-      <c r="B11" t="n">
-        <v>54544.79</v>
-      </c>
-      <c r="C11" t="n">
-        <v>54085.88</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="E11" t="n">
-        <v>5.72</v>
-      </c>
-      <c r="F11" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>46240</v>
-      </c>
-      <c r="B12" t="n">
-        <v>53885.1</v>
-      </c>
-      <c r="C12" t="n">
-        <v>54349.12</v>
-      </c>
-      <c r="D12" t="n">
-        <v>-0.85</v>
-      </c>
-      <c r="E12" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="F12" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>46241</v>
-      </c>
-      <c r="B13" t="n">
-        <v>53987.31</v>
-      </c>
-      <c r="C13" t="n">
-        <v>53885.1</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E13" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="G13" t="n">
-        <v>-0.14</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>46244</v>
-      </c>
-      <c r="B14" t="n">
-        <v>53969.28</v>
-      </c>
-      <c r="C14" t="n">
-        <v>54036.93</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="F14" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.14</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>46245</v>
-      </c>
-      <c r="B15" t="n">
-        <v>54016.06</v>
-      </c>
-      <c r="C15" t="n">
-        <v>53975.98</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E15" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="F15" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>46246</v>
-      </c>
-      <c r="B16" t="n">
-        <v>53795.51</v>
-      </c>
-      <c r="C16" t="n">
-        <v>53791.85</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E16" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="F16" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>46247</v>
-      </c>
-      <c r="B17" t="n">
-        <v>53964.83</v>
-      </c>
-      <c r="C17" t="n">
-        <v>53770.27</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="F17" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>46248</v>
-      </c>
-      <c r="B18" t="n">
-        <v>53804.83</v>
-      </c>
-      <c r="C18" t="n">
-        <v>53839.99</v>
-      </c>
-      <c r="D18" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="E18" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="F18" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>46251</v>
-      </c>
-      <c r="C19" t="n">
-        <v>53732.41</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>46252</v>
-      </c>
-      <c r="B20" t="n">
-        <v>53343.4</v>
-      </c>
-      <c r="C20" t="n">
-        <v>53459.78</v>
-      </c>
-      <c r="D20" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="E20" t="n">
-        <v>-0.83</v>
-      </c>
-      <c r="F20" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="G20" t="n">
-        <v>-0.49</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>46253</v>
-      </c>
-      <c r="B21" t="n">
-        <v>53463.05</v>
-      </c>
-      <c r="C21" t="n">
-        <v>53343.4</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E21" t="n">
-        <v>-0.57</v>
-      </c>
-      <c r="F21" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>46254</v>
-      </c>
-      <c r="B22" t="n">
-        <v>52759.21</v>
-      </c>
-      <c r="C22" t="n">
-        <v>53463.05</v>
-      </c>
-      <c r="D22" t="n">
-        <v>-1.32</v>
-      </c>
-      <c r="E22" t="n">
-        <v>-2.01</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="G22" t="n">
-        <v>-0.38</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>46255</v>
-      </c>
-      <c r="B23" t="n">
-        <v>53277.01</v>
-      </c>
-      <c r="C23" t="n">
-        <v>52759.21</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="E23" t="n">
-        <v>-0.85</v>
-      </c>
-      <c r="F23" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>46258</v>
-      </c>
-      <c r="B24" t="n">
-        <v>53417.16</v>
-      </c>
-      <c r="C24" t="n">
-        <v>53277.01</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E24" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="F24" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="G24" t="n">
-        <v>-0.08</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>46259</v>
-      </c>
-      <c r="B25" t="n">
-        <v>53577.4</v>
-      </c>
-      <c r="C25" t="n">
-        <v>53417.16</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="F25" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>46260</v>
-      </c>
-      <c r="B26" t="n">
-        <v>53463.88</v>
-      </c>
-      <c r="C26" t="n">
-        <v>53577.4</v>
-      </c>
-      <c r="D26" t="n">
-        <v>-0.21</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="G26" t="n">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>46261</v>
-      </c>
-      <c r="B27" t="n">
-        <v>53569.44</v>
-      </c>
-      <c r="C27" t="n">
-        <v>53463.88</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E27" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="F27" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.87</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>46262</v>
-      </c>
-      <c r="B28" t="n">
-        <v>53559.99</v>
-      </c>
-      <c r="C28" t="n">
-        <v>53569.44</v>
-      </c>
-      <c r="D28" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="F28" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="B29" t="n">
-        <v>53212.7</v>
-      </c>
-      <c r="C29" t="n">
-        <v>53559.99</v>
-      </c>
-      <c r="D29" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="E29" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="F29" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="G29" t="n">
-        <v>-0.71</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B30" t="n">
-        <v>52960.85</v>
-      </c>
-      <c r="C30" t="n">
-        <v>53185.9</v>
-      </c>
-      <c r="D30" t="n">
-        <v>-0.42</v>
-      </c>
-      <c r="E30" t="n">
-        <v>-0.85</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="G30" t="n">
-        <v>-0.73</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>46267</v>
-      </c>
-      <c r="B31" t="n">
-        <v>53171.82</v>
-      </c>
-      <c r="C31" t="n">
-        <v>52766.88</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E31" t="n">
-        <v>-0.55</v>
-      </c>
-      <c r="F31" t="n">
-        <v>-1.69</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0.71</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>46268</v>
-      </c>
-      <c r="B32" t="n">
-        <v>53412.4</v>
-      </c>
-      <c r="C32" t="n">
-        <v>53061.95</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="E32" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="F32" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="G32" t="n">
-        <v>2.74</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="n">
-        <v>46269</v>
-      </c>
-      <c r="B33" t="n">
         <v>53409.5</v>
       </c>
       <c r="C33" t="n">
@@ -7274,7 +7317,7 @@
         <v>52002.41</v>
       </c>
       <c r="D63" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E63" t="n">
         <v>0.29</v>
@@ -7284,6 +7327,29 @@
       </c>
       <c r="G63" t="n">
         <v>-0.16</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B64" t="n">
+        <v>52472.73</v>
+      </c>
+      <c r="C64" t="n">
+        <v>51966.03</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="E64" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-0.05</v>
       </c>
     </row>
   </sheetData>
@@ -8577,9 +8643,6 @@
       <c r="F62" t="n">
         <v>20.18</v>
       </c>
-      <c r="G62" t="n">
-        <v/>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
